--- a/working-example/baseball/DGF.xlsx
+++ b/working-example/baseball/DGF.xlsx
@@ -173,6 +173,9 @@
   </si>
   <si>
     <t xml:space="preserve">text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">name.person</t>
   </si>
   <si>
     <t xml:space="preserve">no</t>
@@ -317,60 +320,6 @@
     <t xml:space="preserve">Player's last name</t>
   </si>
   <si>
-    <t xml:space="preserve">[ 
-  {  "level" :  "Johnson"  ,  "label" :  "Johnson"  }, 
-  {  "level" :  "Perez"  ,  "label" :  "Perez"  }, 
-  {  "level" :  "Martinez"  ,  "label" :  "Martinez"  }, 
-  {  "level" :  "Jones"  ,  "label" :  "Jones"  }, 
-  {  "level" :  "Davis"  ,  "label" :  "Davis"  }, 
-  {  "level" :  "Wilson"  ,  "label" :  "Wilson"  }, 
-  {  "level" :  "Hernandez"  ,  "label" :  "Hernandez"  }, 
-  {  "level" :  "Rodriguez"  ,  "label" :  "Rodriguez"  }, 
-  {  "level" :  "Smith"  ,  "label" :  "Smith"  }, 
-  {  "level" :  "Williams"  ,  "label" :  "Williams"  }, 
-  {  "level" :  "Gonzalez"  ,  "label" :  "Gonzalez"  }, 
-  {  "level" :  "Ramirez"  ,  "label" :  "Ramirez"  }, 
-  {  "level" :  "Young"  ,  "label" :  "Young"  }, 
-  {  "level" :  "Anderson"  ,  "label" :  "Anderson"  }, 
-  {  "level" :  "Brown"  ,  "label" :  "Brown"  }, 
-  {  "level" :  "Miller"  ,  "label" :  "Miller"  }, 
-  {  "level" :  "Garcia"  ,  "label" :  "Garcia"  }, 
-  {  "level" :  "Sanchez"  ,  "label" :  "Sanchez"  }, 
-  {  "level" :  "Castillo"  ,  "label" :  "Castillo"  }, 
-  {  "level" :  "Cruz"  ,  "label" :  "Cruz"  }, 
-  {  "level" :  "Jackson"  ,  "label" :  "Jackson"  }, 
-  {  "level" :  "Lopez"  ,  "label" :  "Lopez"  }, 
-  {  "level" :  "Thompson"  ,  "label" :  "Thompson"  }, 
-  {  "level" :  "Walker"  ,  "label" :  "Walker"  }, 
-  {  "level" :  "Pena"  ,  "label" :  "Pena"  }, 
-  {  "level" :  "Bell"  ,  "label" :  "Bell"  }, 
-  {  "level" :  "Cabrera"  ,  "label" :  "Cabrera"  }, 
-  {  "level" :  "Clark"  ,  "label" :  "Clark"  }, 
-  {  "level" :  "Hill"  ,  "label" :  "Hill"  }, 
-  {  "level" :  "Reed"  ,  "label" :  "Reed"  }, 
-  {  "level" :  "Diaz"  ,  "label" :  "Diaz"  }, 
-  {  "level" :  "Harris"  ,  "label" :  "Harris"  }, 
-  {  "level" :  "Moore"  ,  "label" :  "Moore"  }, 
-  {  "level" :  "Ortiz"  ,  "label" :  "Ortiz"  }, 
-  {  "level" :  "Rivera"  ,  "label" :  "Rivera"  }, 
-  {  "level" :  "White"  ,  "label" :  "White"  }, 
-  {  "level" :  "Wright"  ,  "label" :  "Wright"  }, 
-  {  "level" :  "Alvarez"  ,  "label" :  "Alvarez"  }, 
-  {  "level" :  "Green"  ,  "label" :  "Green"  }, 
-  {  "level" :  "Lee"  ,  "label" :  "Lee"  }, 
-  {  "level" :  "Murphy"  ,  "label" :  "Murphy"  }, 
-  {  "level" :  "Wood"  ,  "label" :  "Wood"  }, 
-  {  "level" :  "Adams"  ,  "label" :  "Adams"  }, 
-  {  "level" :  "Hall"  ,  "label" :  "Hall"  }, 
-  {  "level" :  "Lewis"  ,  "label" :  "Lewis"  }, 
-  {  "level" :  "Morris"  ,  "label" :  "Morris"  }, 
-  {  "level" :  "Myers"  ,  "label" :  "Myers"  }, 
-  {  "level" :  "Patterson"  ,  "label" :  "Patterson"  }, 
-  {  "level" :  "Powell"  ,  "label" :  "Powell"  }, 
-  {  "level" :  "Reyes"  ,  "label" :  "Reyes"  }
-]</t>
-  </si>
-  <si>
     <t xml:space="preserve">Aardsma ;; 
 Aase ;; 
 Abad ;; 
@@ -378,16 +327,7 @@
 Abercrombie</t>
   </si>
   <si>
-    <t xml:space="preserve">geographic {{ mutually_exclusive :: categorical }}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">categorical:mutually_exclusive:geographic</t>
-  </si>
-  <si>
     <t xml:space="preserve">categorical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mutually_exclusive.geographic</t>
   </si>
   <si>
     <t xml:space="preserve">[ 
@@ -399,82 +339,118 @@
     <t xml:space="preserve">Johnson ;; Perez ;; Martinez ;; Jones ;; Davis ;; Wilson ;; Hernandez ;; Rodriguez ;; Smith ;; Williams ;; Gonzalez ;; Ramirez ;; Young ;; Anderson ;; Brown ;; Miller ;; Garcia ;; Sanchez ;; Castillo ;; Cruz ;; Jackson ;; Lopez ;; Thompson ;; Walker ;; Pena ;; Bell ;; Cabrera ;; Clark ;; Hill ;; Reed ;; Diaz ;; Harris ;; Moore ;; Ortiz ;; Rivera ;; White ;; Wright ;; Alvarez ;; Green ;; Lee ;; Mur</t>
   </si>
   <si>
+    <t xml:space="preserve">{
+  "STATS": [
+    {
+      "STAT": "Minimum",
+      "CHARACTERS": 2,
+      "WORDS": 1
+    },
+    {
+      "STAT": "Median",
+      "CHARACTERS": 6,
+      "WORDS": 1
+    },
+    {
+      "STAT": "Mean",
+      "CHARACTERS": 6.49,
+      "WORDS": 1.01
+    },
+    {
+      "STAT": "Max",
+      "CHARACTERS": 14,
+      "WORDS": 3
+    },
+    {
+      "STAT": "Skew",
+      "CHARACTERS": 0.5,
+      "WORDS": 17.05
+    }
+  ],
+  "HIST": [
+    "&lt;?xml version=\"1.0\" encoding=\"UTF-8\"?&gt;\n&lt;svg xmlns=\"http://www.w3.org/2000/svg\" xmlns:xlink=\"http://www.w3.org/1999/xlink\" width=\"48.00pt\" height=\"12.00pt\" viewBox=\"0 0 48.00 12.00\"&gt;\n  &lt;g class=\"svglite\"&gt;\n    &lt;defs&gt;\n      &lt;style type=\"text/css\"&gt;&lt;![CDATA[\n    .svglite line, .svglite polyline, .svglite polygon, .svglite path, .svglite rect, .svglite circle {\n      fill: none;\n      stroke: #000000;\n      stroke-linecap: round;\n      stroke-linejoin: round;\n      stroke-miterlimit: 10.00;\n    }\n    .svglite text {\n      white-space: pre;\n    }\n    .svglite g.glyphgroup path {\n      fill: inherit;\n      stroke: none;\n    }\n  ]]&gt;&lt;\/style&gt;\n    &lt;\/defs&gt;\n    &lt;rect width=\"100%\" height=\"100%\" style=\"stroke: none; fill: none;\"/&gt;\n    &lt;defs&gt;\n      &lt;clipPath id=\"cpMC4wMHw0OC4wMHwwLjAwfDEyLjAw\"&gt;\n        &lt;rect x=\"0.00\" y=\"0.00\" width=\"48.00\" height=\"12.00\"/&gt;\n      &lt;\/clipPath&gt;\n    &lt;\/defs&gt;\n    &lt;g clip-path=\"url(#cpMC4wMHw0OC4wMHwwLjAwfDEyLjAw)\"&gt;\n&lt;\/g&gt;\n    &lt;defs&gt;\n      &lt;clipPath id=\"cpMC4wMHw0OC4wMHwyLjg4fDEyLjAw\"&gt;\n        &lt;rect x=\"0.00\" y=\"2.88\" width=\"48.00\" height=\"9.12\"/&gt;\n      &lt;\/clipPath&gt;\n    &lt;\/defs&gt;\n    &lt;g clip-path=\"url(#cpMC4wMHw0OC4wMHwyLjg4fDEyLjAw)\"&gt;\n      &lt;rect x=\"1.78\" y=\"11.22\" width=\"3.70\" height=\"0.44\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"5.48\" y=\"8.63\" width=\"3.70\" height=\"3.03\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"9.19\" y=\"5.07\" width=\"3.70\" height=\"6.59\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"12.89\" y=\"3.22\" width=\"3.70\" height=\"8.44\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"16.59\" y=\"4.64\" width=\"3.70\" height=\"7.03\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"20.30\" y=\"6.82\" width=\"3.70\" height=\"4.84\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"24.00\" y=\"9.18\" width=\"3.70\" height=\"2.48\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"27.70\" y=\"10.78\" width=\"3.70\" height=\"0.88\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"31.41\" y=\"11.22\" width=\"3.70\" height=\"0.45\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"35.11\" y=\"11.59\" width=\"3.70\" height=\"0.074\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"38.81\" y=\"11.62\" width=\"3.70\" height=\"0.045\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"42.52\" y=\"11.65\" width=\"3.70\" height=\"0.015\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n    &lt;\/g&gt;\n  &lt;\/g&gt;\n&lt;\/svg&gt;\n",
+    "&lt;?xml version=\"1.0\" encoding=\"UTF-8\"?&gt;\n&lt;svg xmlns=\"http://www.w3.org/2000/svg\" xmlns:xlink=\"http://www.w3.org/1999/xlink\" width=\"48.00pt\" height=\"12.00pt\" viewBox=\"0 0 48.00 12.00\"&gt;\n  &lt;g class=\"svglite\"&gt;\n    &lt;defs&gt;\n      &lt;style type=\"text/css\"&gt;&lt;![CDATA[\n    .svglite line, .svglite polyline, .svglite polygon, .svglite path, .svglite rect, .svglite circle {\n      fill: none;\n      stroke: #000000;\n      stroke-linecap: round;\n      stroke-linejoin: round;\n      stroke-miterlimit: 10.00;\n    }\n    .svglite text {\n      white-space: pre;\n    }\n    .svglite g.glyphgroup path {\n      fill: inherit;\n      stroke: none;\n    }\n  ]]&gt;&lt;\/style&gt;\n    &lt;\/defs&gt;\n    &lt;rect width=\"100%\" height=\"100%\" style=\"stroke: none; fill: none;\"/&gt;\n    &lt;defs&gt;\n      &lt;clipPath id=\"cpMC4wMHw0OC4wMHwwLjAwfDEyLjAw\"&gt;\n        &lt;rect x=\"0.00\" y=\"0.00\" width=\"48.00\" height=\"12.00\"/&gt;\n      &lt;\/clipPath&gt;\n    &lt;\/defs&gt;\n    &lt;g clip-path=\"url(#cpMC4wMHw0OC4wMHwwLjAwfDEyLjAw)\"&gt;\n&lt;\/g&gt;\n    &lt;defs&gt;\n      &lt;clipPath id=\"cpMC4wMHw0OC4wMHwyLjg4fDEyLjAw\"&gt;\n        &lt;rect x=\"0.00\" y=\"2.88\" width=\"48.00\" height=\"9.12\"/&gt;\n      &lt;\/clipPath&gt;\n    &lt;\/defs&gt;\n    &lt;g clip-path=\"url(#cpMC4wMHw0OC4wMHwyLjg4fDEyLjAw)\"&gt;\n      &lt;rect x=\"1.78\" y=\"3.22\" width=\"4.44\" height=\"8.44\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"6.22\" y=\"11.66\" width=\"4.44\" height=\"0.00\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"10.67\" y=\"11.66\" width=\"4.44\" height=\"0.00\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"15.11\" y=\"11.66\" width=\"4.44\" height=\"0.00\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"19.56\" y=\"11.63\" width=\"4.44\" height=\"0.033\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"24.00\" y=\"11.66\" width=\"4.44\" height=\"0.00\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"28.44\" y=\"11.66\" width=\"4.44\" height=\"0.00\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"32.89\" y=\"11.66\" width=\"4.44\" height=\"0.00\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"37.33\" y=\"11.66\" width=\"4.44\" height=\"0.00\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"41.78\" y=\"11.65\" width=\"4.44\" height=\"0.0073\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n    &lt;\/g&gt;\n  &lt;\/g&gt;\n&lt;\/svg&gt;\n"
+  ],
+  "COMMON": [
+    {
+      "Value": "Johnson",
+      "Frequency": 28
+    },
+    {
+      "Value": "Perez",
+      "Frequency": 28
+    },
+    {
+      "Value": "Martinez",
+      "Frequency": 26
+    },
+    {
+      "Value": "Jones",
+      "Frequency": 25
+    },
+    {
+      "Value": "Davis",
+      "Frequency": 24
+    },
+    {
+      "Value": "Wilson",
+      "Frequency": 24
+    }
+  ]
+}</t>
+  </si>
+  <si>
     <t xml:space="preserve">[ 
-  {  "Value" :  "Johnson"  ,  "Frequency" :  28  }, 
-  {  "Value" :  "Perez"  ,  "Frequency" :  28  }, 
-  {  "Value" :  "Martinez"  ,  "Frequency" :  26  }, 
-  {  "Value" :  "Jones"  ,  "Frequency" :  25  }, 
-  {  "Value" :  "Davis"  ,  "Frequency" :  24  }, 
-  {  "Value" :  "Wilson"  ,  "Frequency" :  24  }, 
-  {  "Value" :  "Hernandez"  ,  "Frequency" :  21  }, 
-  {  "Value" :  "Rodriguez"  ,  "Frequency" :  19  }, 
-  {  "Value" :  "Smith"  ,  "Frequency" :  19  }, 
-  {  "Value" :  "Williams"  ,  "Frequency" :  19  }, 
-  {  "Value" :  "Gonzalez"  ,  "Frequency" :  18  }, 
-  {  "Value" :  "Ramirez"  ,  "Frequency" :  18  }, 
-  {  "Value" :  "Young"  ,  "Frequency" :  17  }, 
-  {  "Value" :  "Anderson"  ,  "Frequency" :  16  }, 
-  {  "Value" :  "Brown"  ,  "Frequency" :  16  }, 
-  {  "Value" :  "Miller"  ,  "Frequency" :  16  }, 
-  {  "Value" :  "Garcia"  ,  "Frequency" :  15  }, 
-  {  "Value" :  "Sanchez"  ,  "Frequency" :  14  }, 
-  {  "Value" :  "Castillo"  ,  "Frequency" :  12  }, 
-  {  "Value" :  "Cruz"  ,  "Frequency" :  12  }, 
-  {  "Value" :  "Jackson"  ,  "Frequency" :  12  }, 
-  {  "Value" :  "Lopez"  ,  "Frequency" :  12  }, 
-  {  "Value" :  "Thompson"  ,  "Frequency" :  12  }, 
-  {  "Value" :  "Walker"  ,  "Frequency" :  12  }, 
-  {  "Value" :  "Pena"  ,  "Frequency" :  11  }, 
-  {  "Value" :  "Bell"  ,  "Frequency" :  10  }, 
-  {  "Value" :  "Cabrera"  ,  "Frequency" :  10  }, 
-  {  "Value" :  "Clark"  ,  "Frequency" :  10  }, 
-  {  "Value" :  "Hill"  ,  "Frequency" :  10  }, 
-  {  "Value" :  "Reed"  ,  "Frequency" :  10  }, 
-  {  "Value" :  "Diaz"  ,  "Frequency" :  9  }, 
-  {  "Value" :  "Harris"  ,  "Frequency" :  9  }, 
-  {  "Value" :  "Moore"  ,  "Frequency" :  9  }, 
-  {  "Value" :  "Ortiz"  ,  "Frequency" :  9  }, 
-  {  "Value" :  "Rivera"  ,  "Frequency" :  9  }, 
-  {  "Value" :  "White"  ,  "Frequency" :  9  }, 
-  {  "Value" :  "Wright"  ,  "Frequency" :  9  }, 
-  {  "Value" :  "Alvarez"  ,  "Frequency" :  8  }, 
-  {  "Value" :  "Green"  ,  "Frequency" :  8  }, 
-  {  "Value" :  "Lee"  ,  "Frequency" :  8  }, 
-  {  "Value" :  "Murphy"  ,  "Frequency" :  8  }, 
-  {  "Value" :  "Wood"  ,  "Frequency" :  8  }, 
-  {  "Value" :  "Adams"  ,  "Frequency" :  7  }, 
-  {  "Value" :  "Hall"  ,  "Frequency" :  7  }, 
-  {  "Value" :  "Lewis"  ,  "Frequency" :  7  }, 
-  {  "Value" :  "Morris"  ,  "Frequency" :  7  }, 
-  {  "Value" :  "Myers"  ,  "Frequency" :  7  }, 
-  {  "Value" :  "Patterson"  ,  "Frequency" :  7  }, 
-  {  "Value" :  "Powell"  ,  "Frequency" :  7  }, 
-  {  "Value" :  "Reyes"  ,  "Frequency" :  7  }
-]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 
-  {  "x" :  "Johnson"  ,  "Freq" :  28  }, 
-  {  "x" :  "Perez"  ,  "Freq" :  28  }, 
-  {  "x" :  "Martinez"  ,  "Freq" :  26  }, 
-  {  "x" :  "Jones"  ,  "Freq" :  25  }, 
-  {  "x" :  "Davis"  ,  "Freq" :  24  }, 
-  {  "x" :  "Wilson"  ,  "Freq" :  24  }, 
-  {  "x" :  "Hernandez"  ,  "Freq" :  21  }, 
-  {  "x" :  "Rodriguez"  ,  "Freq" :  19  }, 
-  {  "x" :  "Smith"  ,  "Freq" :  19  }, 
-  {  "x" :  "Williams"  ,  "Freq" :  19  }, 
-  {  "x" :  "Gonzalez"  ,  "Freq" :  18  }, 
-  {  "x" :  "Ramirez"  ,  "Freq" :  18  }, 
-  {  "x" :  "Young"  ,  "Freq" :  17  }, 
-  {  "x" :  "Anderson"  ,  "Freq" :  16  }, 
-  {  "x" :  "Brown"  ,  "Freq" :  16  }, 
-  {  "x" :  "Miller"  ,  "Freq" :  16  }, 
-  {  "x" :  "Garcia"  ,  "Freq" :  15  }, 
-  {  "x" :  "Sanchez"  ,  "Freq" :  14  }, 
-  {  "x" :  "Castillo"  ,  "Freq" :  12  }, 
-  {  "x" :  "Cruz"  ,  "Freq" :  12  }, 
-  {  "x" :  "other"  ,  "Freq" :  4233  }
+  {  "ww" :  "Johnson"  ,  "Freq" :  28  }, 
+  {  "ww" :  "Perez"  ,  "Freq" :  28  }, 
+  {  "ww" :  "Martinez"  ,  "Freq" :  26  }, 
+  {  "ww" :  "Jones"  ,  "Freq" :  25  }, 
+  {  "ww" :  "Davis"  ,  "Freq" :  24  }, 
+  {  "ww" :  "Wilson"  ,  "Freq" :  24  }, 
+  {  "ww" :  "Hernandez"  ,  "Freq" :  21  }, 
+  {  "ww" :  "Rodriguez"  ,  "Freq" :  19  }, 
+  {  "ww" :  "Smith"  ,  "Freq" :  19  }, 
+  {  "ww" :  "Williams"  ,  "Freq" :  19  }, 
+  {  "ww" :  "Gonzalez"  ,  "Freq" :  18  }, 
+  {  "ww" :  "Ramirez"  ,  "Freq" :  18  }, 
+  {  "ww" :  "Young"  ,  "Freq" :  17  }, 
+  {  "ww" :  "Anderson"  ,  "Freq" :  16  }, 
+  {  "ww" :  "Brown"  ,  "Freq" :  16  }, 
+  {  "ww" :  "Miller"  ,  "Freq" :  16  }, 
+  {  "ww" :  "Garcia"  ,  "Freq" :  15  }, 
+  {  "ww" :  "Sanchez"  ,  "Freq" :  14  }, 
+  {  "ww" :  "Castillo"  ,  "Freq" :  12  }, 
+  {  "ww" :  "Cruz"  ,  "Freq" :  12  }, 
+  {  "ww" :  "Jackson"  ,  "Freq" :  12  }, 
+  {  "ww" :  "Lopez"  ,  "Freq" :  12  }, 
+  {  "ww" :  "Thompson"  ,  "Freq" :  12  }, 
+  {  "ww" :  "Walker"  ,  "Freq" :  12  }, 
+  {  "ww" :  "Pena"  ,  "Freq" :  11  }, 
+  {  "ww" :  "Bell"  ,  "Freq" :  10  }, 
+  {  "ww" :  "Cabrera"  ,  "Freq" :  10  }, 
+  {  "ww" :  "Clark"  ,  "Freq" :  10  }, 
+  {  "ww" :  "Hill"  ,  "Freq" :  10  }, 
+  {  "ww" :  "Reed"  ,  "Freq" :  10  }, 
+  {  "ww" :  "Diaz"  ,  "Freq" :  9  }, 
+  {  "ww" :  "Harris"  ,  "Freq" :  9  }, 
+  {  "ww" :  "Moore"  ,  "Freq" :  9  }, 
+  {  "ww" :  "Ortiz"  ,  "Freq" :  9  }, 
+  {  "ww" :  "Rivera"  ,  "Freq" :  9  }, 
+  {  "ww" :  "White"  ,  "Freq" :  9  }, 
+  {  "ww" :  "Wright"  ,  "Freq" :  9  }, 
+  {  "ww" :  "Alvarez"  ,  "Freq" :  8  }, 
+  {  "ww" :  "Green"  ,  "Freq" :  8  }, 
+  {  "ww" :  "Lee"  ,  "Freq" :  8  }, 
+  {  "ww" :  "Murphy"  ,  "Freq" :  8  }, 
+  {  "ww" :  "Wood"  ,  "Freq" :  8  }, 
+  {  "ww" :  "Adams"  ,  "Freq" :  7  }, 
+  {  "ww" :  "Hall"  ,  "Freq" :  7  }, 
+  {  "ww" :  "Lewis"  ,  "Freq" :  7  }, 
+  {  "ww" :  "Morris"  ,  "Freq" :  7  }, 
+  {  "ww" :  "Myers"  ,  "Freq" :  7  }, 
+  {  "ww" :  "Patterson"  ,  "Freq" :  7  }, 
+  {  "ww" :  "Powell"  ,  "Freq" :  7  }, 
+  {  "ww" :  "Reyes"  ,  "Freq" :  7  }
 ]</t>
   </si>
   <si>
@@ -728,6 +704,60 @@
     <t xml:space="preserve">State or province where the player was born: a two-letter postal code for US states, a region name elsewhere (e.g. La Romana); blank if unknown</t>
   </si>
   <si>
+    <t xml:space="preserve">[ 
+  {  "level" :  "CA"  ,  "label" :  "CA"  }, 
+  {  "level" :  "TX"  ,  "label" :  "TX"  }, 
+  {  "level" :  "FL"  ,  "label" :  "FL"  }, 
+  {  "level" :  "NY"  ,  "label" :  "NY"  }, 
+  {  "level" :  "IL"  ,  "label" :  "IL"  }, 
+  {  "level" :  "OH"  ,  "label" :  "OH"  }, 
+  {  "level" :  "PA"  ,  "label" :  "PA"  }, 
+  {  "level" :  "GA"  ,  "label" :  "GA"  }, 
+  {  "level" :  "Distrito Nacional"  ,  "label" :  "Distrito Nacional"  }, 
+  {  "level" :  "MI"  ,  "label" :  "MI"  }, 
+  {  "level" :  "VA"  ,  "label" :  "VA"  }, 
+  {  "level" :  "LA"  ,  "label" :  "LA"  }, 
+  {  "level" :  "NJ"  ,  "label" :  "NJ"  }, 
+  {  "level" :  "NC"  ,  "label" :  "NC"  }, 
+  {  "level" :  "IN"  ,  "label" :  "IN"  }, 
+  {  "level" :  "MO"  ,  "label" :  "MO"  }, 
+  {  "level" :  "TN"  ,  "label" :  "TN"  }, 
+  {  "level" :  "AL"  ,  "label" :  "AL"  }, 
+  {  "level" :  "WA"  ,  "label" :  "WA"  }, 
+  {  "level" :  "MA"  ,  "label" :  "MA"  }, 
+  {  "level" :  "San Pedro de Macoris"  ,  "label" :  "San Pedro de Macoris"  }, 
+  {  "level" :  "KY"  ,  "label" :  "KY"  }, 
+  {  "level" :  "OK"  ,  "label" :  "OK"  }, 
+  {  "level" :  "MS"  ,  "label" :  "MS"  }, 
+  {  "level" :  "SC"  ,  "label" :  "SC"  }, 
+  {  "level" :  "OR"  ,  "label" :  "OR"  }, 
+  {  "level" :  "MD"  ,  "label" :  "MD"  }, 
+  {  "level" :  "AZ"  ,  "label" :  "AZ"  }, 
+  {  "level" :  "San Cristobal"  ,  "label" :  "San Cristobal"  }, 
+  {  "level" :  "Carabobo"  ,  "label" :  "Carabobo"  }, 
+  {  "level" :  "CT"  ,  "label" :  "CT"  }, 
+  {  "level" :  "MN"  ,  "label" :  "MN"  }, 
+  {  "level" :  "Distrito Federal"  ,  "label" :  "Distrito Federal"  }, 
+  {  "level" :  "IA"  ,  "label" :  "IA"  }, 
+  {  "level" :  "KS"  ,  "label" :  "KS"  }, 
+  {  "level" :  "WI"  ,  "label" :  "WI"  }, 
+  {  "level" :  "Zulia"  ,  "label" :  "Zulia"  }, 
+  {  "level" :  "CO"  ,  "label" :  "CO"  }, 
+  {  "level" :  "HI"  ,  "label" :  "HI"  }, 
+  {  "level" :  "ON"  ,  "label" :  "ON"  }, 
+  {  "level" :  "Peravia"  ,  "label" :  "Peravia"  }, 
+  {  "level" :  "Santiago"  ,  "label" :  "Santiago"  }, 
+  {  "level" :  "NV"  ,  "label" :  "NV"  }, 
+  {  "level" :  "BC"  ,  "label" :  "BC"  }, 
+  {  "level" :  "La Habana"  ,  "label" :  "La Habana"  }, 
+  {  "level" :  "Anzoategui"  ,  "label" :  "Anzoategui"  }, 
+  {  "level" :  "AR"  ,  "label" :  "AR"  }, 
+  {  "level" :  "Aragua"  ,  "label" :  "Aragua"  }, 
+  {  "level" :  "NE"  ,  "label" :  "NE"  }, 
+  {  "level" :  "Bolivar"  ,  "label" :  "Bolivar"  }
+]</t>
+  </si>
+  <si>
     <t xml:space="preserve">CO ;; 
 CA ;; 
 La Romana ;; 
@@ -735,6 +765,15 @@
 MI</t>
   </si>
   <si>
+    <t xml:space="preserve">geographic {{ mutually_exclusive :: categorical }}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">categorical:mutually_exclusive:geographic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mutually_exclusive.geographic</t>
+  </si>
+  <si>
     <t xml:space="preserve">[ 
   {  "STAT" :  "Rows"  ,  "VAL" :  "4,620"  ,  "PER" :  ""  }, 
   {  "STAT" :  "Distinct"  ,  "VAL" :  "210"  ,  "PER" :  "(4.5%)"  }, 
@@ -745,118 +784,71 @@
     <t xml:space="preserve">CA ;; TX ;; FL ;; NY ;; IL ;; OH ;; PA ;; GA ;; Distrito Nacional ;; MI ;; VA ;; LA ;; NJ ;; NC ;; IN ;; MO ;; TN ;; AL ;; WA ;; MA ;; San Pedro de Macoris ;; KY ;; OK ;; MS ;; SC ;; OR ;; MD ;; AZ ;; San Cristobal ;; Carabobo ;; CT ;; MN ;; Distrito Federal ;; IA ;; KS ;; WI ;; Zulia ;; CO ;; HI ;; ON ;; Peravia ;; Santiago ;; NV ;; BC ;; La Habana ;; Anzoategui ;; AR ;; Aragua ;; NE ;; Bolivar</t>
   </si>
   <si>
-    <t xml:space="preserve">{
-  "STATS": [
-    {
-      "STAT": "Minimum",
-      "CHARACTERS": 2,
-      "WORDS": 1
-    },
-    {
-      "STAT": "Median",
-      "CHARACTERS": 2,
-      "WORDS": 1
-    },
-    {
-      "STAT": "Mean",
-      "CHARACTERS": 3.63,
-      "WORDS": 1.12
-    },
-    {
-      "STAT": "Max",
-      "CHARACTERS": 22,
-      "WORDS": 4
-    },
-    {
-      "STAT": "Skew",
-      "CHARACTERS": 2.65,
-      "WORDS": 4.45
-    }
-  ],
-  "HIST": [
-    "&lt;?xml version=\"1.0\" encoding=\"UTF-8\"?&gt;\n&lt;svg xmlns=\"http://www.w3.org/2000/svg\" xmlns:xlink=\"http://www.w3.org/1999/xlink\" width=\"48.00pt\" height=\"12.00pt\" viewBox=\"0 0 48.00 12.00\"&gt;\n  &lt;g class=\"svglite\"&gt;\n    &lt;defs&gt;\n      &lt;style type=\"text/css\"&gt;&lt;![CDATA[\n    .svglite line, .svglite polyline, .svglite polygon, .svglite path, .svglite rect, .svglite circle {\n      fill: none;\n      stroke: #000000;\n      stroke-linecap: round;\n      stroke-linejoin: round;\n      stroke-miterlimit: 10.00;\n    }\n    .svglite text {\n      white-space: pre;\n    }\n    .svglite g.glyphgroup path {\n      fill: inherit;\n      stroke: none;\n    }\n  ]]&gt;&lt;\/style&gt;\n    &lt;\/defs&gt;\n    &lt;rect width=\"100%\" height=\"100%\" style=\"stroke: none; fill: none;\"/&gt;\n    &lt;defs&gt;\n      &lt;clipPath id=\"cpMC4wMHw0OC4wMHwwLjAwfDEyLjAw\"&gt;\n        &lt;rect x=\"0.00\" y=\"0.00\" width=\"48.00\" height=\"12.00\"/&gt;\n      &lt;\/clipPath&gt;\n    &lt;\/defs&gt;\n    &lt;g clip-path=\"url(#cpMC4wMHw0OC4wMHwwLjAwfDEyLjAw)\"&gt;\n&lt;\/g&gt;\n    &lt;defs&gt;\n      &lt;clipPath id=\"cpMC4wMHw0OC4wMHwyLjg4fDEyLjAw\"&gt;\n        &lt;rect x=\"0.00\" y=\"2.88\" width=\"48.00\" height=\"9.12\"/&gt;\n      &lt;\/clipPath&gt;\n    &lt;\/defs&gt;\n    &lt;g clip-path=\"url(#cpMC4wMHw0OC4wMHwyLjg4fDEyLjAw)\"&gt;\n      &lt;rect x=\"1.78\" y=\"3.22\" width=\"4.44\" height=\"8.44\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"6.22\" y=\"11.33\" width=\"4.44\" height=\"0.33\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"10.67\" y=\"11.17\" width=\"4.44\" height=\"0.49\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"15.11\" y=\"11.41\" width=\"4.44\" height=\"0.25\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"19.56\" y=\"11.59\" width=\"4.44\" height=\"0.074\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"24.00\" y=\"11.49\" width=\"4.44\" height=\"0.17\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"28.44\" y=\"11.51\" width=\"4.44\" height=\"0.15\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"32.89\" y=\"11.44\" width=\"4.44\" height=\"0.22\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"37.33\" y=\"11.52\" width=\"4.44\" height=\"0.14\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"41.78\" y=\"11.65\" width=\"4.44\" height=\"0.016\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n    &lt;\/g&gt;\n  &lt;\/g&gt;\n&lt;\/svg&gt;\n",
-    "&lt;?xml version=\"1.0\" encoding=\"UTF-8\"?&gt;\n&lt;svg xmlns=\"http://www.w3.org/2000/svg\" xmlns:xlink=\"http://www.w3.org/1999/xlink\" width=\"48.00pt\" height=\"12.00pt\" viewBox=\"0 0 48.00 12.00\"&gt;\n  &lt;g class=\"svglite\"&gt;\n    &lt;defs&gt;\n      &lt;style type=\"text/css\"&gt;&lt;![CDATA[\n    .svglite line, .svglite polyline, .svglite polygon, .svglite path, .svglite rect, .svglite circle {\n      fill: none;\n      stroke: #000000;\n      stroke-linecap: round;\n      stroke-linejoin: round;\n      stroke-miterlimit: 10.00;\n    }\n    .svglite text {\n      white-space: pre;\n    }\n    .svglite g.glyphgroup path {\n      fill: inherit;\n      stroke: none;\n    }\n  ]]&gt;&lt;\/style&gt;\n    &lt;\/defs&gt;\n    &lt;rect width=\"100%\" height=\"100%\" style=\"stroke: none; fill: none;\"/&gt;\n    &lt;defs&gt;\n      &lt;clipPath id=\"cpMC4wMHw0OC4wMHwwLjAwfDEyLjAw\"&gt;\n        &lt;rect x=\"0.00\" y=\"0.00\" width=\"48.00\" height=\"12.00\"/&gt;\n      &lt;\/clipPath&gt;\n    &lt;\/defs&gt;\n    &lt;g clip-path=\"url(#cpMC4wMHw0OC4wMHwwLjAwfDEyLjAw)\"&gt;\n&lt;\/g&gt;\n    &lt;defs&gt;\n      &lt;clipPath id=\"cpMC4wMHw0OC4wMHwyLjg4fDEyLjAw\"&gt;\n        &lt;rect x=\"0.00\" y=\"2.88\" width=\"48.00\" height=\"9.12\"/&gt;\n      &lt;\/clipPath&gt;\n    &lt;\/defs&gt;\n    &lt;g clip-path=\"url(#cpMC4wMHw0OC4wMHwyLjg4fDEyLjAw)\"&gt;\n      &lt;rect x=\"1.78\" y=\"3.22\" width=\"2.96\" height=\"8.44\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"4.74\" y=\"11.66\" width=\"2.96\" height=\"0.00\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"7.70\" y=\"11.66\" width=\"2.96\" height=\"0.00\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"10.67\" y=\"11.66\" width=\"2.96\" height=\"0.00\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"13.63\" y=\"10.98\" width=\"2.96\" height=\"0.69\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"16.59\" y=\"11.66\" width=\"2.96\" height=\"0.00\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"19.56\" y=\"11.66\" width=\"2.96\" height=\"0.00\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"22.52\" y=\"11.66\" width=\"2.96\" height=\"0.00\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"25.48\" y=\"11.66\" width=\"2.96\" height=\"0.00\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"28.44\" y=\"11.61\" width=\"2.96\" height=\"0.056\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"31.41\" y=\"11.66\" width=\"2.96\" height=\"0.00\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"34.37\" y=\"11.66\" width=\"2.96\" height=\"0.00\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"37.33\" y=\"11.66\" width=\"2.96\" height=\"0.00\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"40.30\" y=\"11.66\" width=\"2.96\" height=\"0.00\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"43.26\" y=\"11.54\" width=\"2.96\" height=\"0.12\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n    &lt;\/g&gt;\n  &lt;\/g&gt;\n&lt;\/svg&gt;\n"
-  ],
-  "COMMON": [
-    {
-      "Value": "CA",
-      "Frequency": 826
-    },
-    {
-      "Value": "TX",
-      "Frequency": 293
-    },
-    {
-      "Value": "FL",
-      "Frequency": 260
-    },
-    {
-      "Value": "NY",
-      "Frequency": 155
-    },
-    {
-      "Value": "IL",
-      "Frequency": 154
-    },
-    {
-      "Value": "OH",
-      "Frequency": 150
-    }
-  ]
-}</t>
-  </si>
-  <si>
     <t xml:space="preserve">[ 
-  {  "ww" :  "CA"  ,  "Freq" :  826  }, 
-  {  "ww" :  "TX"  ,  "Freq" :  293  }, 
-  {  "ww" :  "FL"  ,  "Freq" :  260  }, 
-  {  "ww" :  "NY"  ,  "Freq" :  155  }, 
-  {  "ww" :  "IL"  ,  "Freq" :  154  }, 
-  {  "ww" :  "OH"  ,  "Freq" :  150  }, 
-  {  "ww" :  "Distrito"  ,  "Freq" :  124  }, 
-  {  "ww" :  "PA"  ,  "Freq" :  124  }, 
-  {  "ww" :  "GA"  ,  "Freq" :  115  }, 
-  {  "ww" :  "San"  ,  "Freq" :  108  }, 
-  {  "ww" :  "Nacional"  ,  "Freq" :  92  }, 
-  {  "ww" :  "MI"  ,  "Freq" :  88  }, 
-  {  "ww" :  "VA"  ,  "Freq" :  76  }, 
-  {  "ww" :  "LA"  ,  "Freq" :  75  }, 
-  {  "ww" :  "NJ"  ,  "Freq" :  75  }, 
-  {  "ww" :  "NC"  ,  "Freq" :  71  }, 
-  {  "ww" :  "MO"  ,  "Freq" :  68  }, 
-  {  "ww" :  "de"  ,  "Freq" :  63  }, 
-  {  "ww" :  "TN"  ,  "Freq" :  62  }, 
-  {  "ww" :  "AL"  ,  "Freq" :  60  }, 
-  {  "ww" :  "WA"  ,  "Freq" :  59  }, 
-  {  "ww" :  "MA"  ,  "Freq" :  58  }, 
-  {  "ww" :  "Macoris"  ,  "Freq" :  58  }, 
-  {  "ww" :  "Pedro"  ,  "Freq" :  58  }, 
-  {  "ww" :  "KY"  ,  "Freq" :  57  }, 
-  {  "ww" :  "OK"  ,  "Freq" :  55  }, 
-  {  "ww" :  "MS"  ,  "Freq" :  54  }, 
-  {  "ww" :  "La"  ,  "Freq" :  49  }, 
-  {  "ww" :  "SC"  ,  "Freq" :  48  }, 
-  {  "ww" :  "MD"  ,  "Freq" :  42  }, 
-  {  "ww" :  "AZ"  ,  "Freq" :  41  }, 
-  {  "ww" :  "Cristobal"  ,  "Freq" :  40  }, 
-  {  "ww" :  "Carabobo"  ,  "Freq" :  36  }, 
-  {  "ww" :  "CT"  ,  "Freq" :  34  }, 
-  {  "ww" :  "MN"  ,  "Freq" :  33  }, 
-  {  "ww" :  "Federal"  ,  "Freq" :  32  }, 
-  {  "ww" :  "IA"  ,  "Freq" :  31  }, 
-  {  "ww" :  "KS"  ,  "Freq" :  29  }, 
-  {  "ww" :  "WI"  ,  "Freq" :  28  }, 
-  {  "ww" :  "Zulia"  ,  "Freq" :  26  }, 
-  {  "ww" :  "Santiago"  ,  "Freq" :  25  }, 
-  {  "ww" :  "CO"  ,  "Freq" :  24  }, 
-  {  "ww" :  "HI"  ,  "Freq" :  23  }, 
-  {  "ww" :  "Peravia"  ,  "Freq" :  22  }, 
-  {  "ww" :  "NV"  ,  "Freq" :  21  }, 
-  {  "ww" :  "BC"  ,  "Freq" :  20  }, 
-  {  "ww" :  "Habana"  ,  "Freq" :  20  }, 
-  {  "ww" :  "Anzoategui"  ,  "Freq" :  19  }, 
-  {  "ww" :  "AR"  ,  "Freq" :  19  }, 
-  {  "ww" :  "Aragua"  ,  "Freq" :  19  }
+  {  "Value" :  "CA"  ,  "Frequency" :  826  }, 
+  {  "Value" :  "TX"  ,  "Frequency" :  293  }, 
+  {  "Value" :  "FL"  ,  "Frequency" :  260  }, 
+  {  "Value" :  "NY"  ,  "Frequency" :  155  }, 
+  {  "Value" :  "IL"  ,  "Frequency" :  154  }, 
+  {  "Value" :  "OH"  ,  "Frequency" :  150  }, 
+  {  "Value" :  "PA"  ,  "Frequency" :  124  }, 
+  {  "Value" :  "GA"  ,  "Frequency" :  115  }, 
+  {  "Value" :  "Distrito Nacional"  ,  "Frequency" :  92  }, 
+  {  "Value" :  "MI"  ,  "Frequency" :  88  }, 
+  {  "Value" :  "VA"  ,  "Frequency" :  76  }, 
+  {  "Value" :  "LA"  ,  "Frequency" :  75  }, 
+  {  "Value" :  "NJ"  ,  "Frequency" :  75  }, 
+  {  "Value" :  "NC"  ,  "Frequency" :  71  }, 
+  {  "Value" :  "IN"  ,  "Frequency" :  70  }, 
+  {  "Value" :  "MO"  ,  "Frequency" :  68  }, 
+  {  "Value" :  "TN"  ,  "Frequency" :  62  }, 
+  {  "Value" :  "AL"  ,  "Frequency" :  60  }, 
+  {  "Value" :  "WA"  ,  "Frequency" :  59  }, 
+  {  "Value" :  "MA"  ,  "Frequency" :  58  }, 
+  {  "Value" :  "San Pedro de Macoris"  ,  "Frequency" :  58  }, 
+  {  "Value" :  "KY"  ,  "Frequency" :  57  }, 
+  {  "Value" :  "OK"  ,  "Frequency" :  55  }, 
+  {  "Value" :  "MS"  ,  "Frequency" :  54  }, 
+  {  "Value" :  "SC"  ,  "Frequency" :  48  }, 
+  {  "Value" :  "OR"  ,  "Frequency" :  45  }, 
+  {  "Value" :  "MD"  ,  "Frequency" :  42  }, 
+  {  "Value" :  "AZ"  ,  "Frequency" :  41  }, 
+  {  "Value" :  "San Cristobal"  ,  "Frequency" :  40  }, 
+  {  "Value" :  "Carabobo"  ,  "Frequency" :  36  }, 
+  {  "Value" :  "CT"  ,  "Frequency" :  34  }, 
+  {  "Value" :  "MN"  ,  "Frequency" :  33  }, 
+  {  "Value" :  "Distrito Federal"  ,  "Frequency" :  32  }, 
+  {  "Value" :  "IA"  ,  "Frequency" :  31  }, 
+  {  "Value" :  "KS"  ,  "Frequency" :  29  }, 
+  {  "Value" :  "WI"  ,  "Frequency" :  28  }, 
+  {  "Value" :  "Zulia"  ,  "Frequency" :  26  }, 
+  {  "Value" :  "CO"  ,  "Frequency" :  24  }, 
+  {  "Value" :  "HI"  ,  "Frequency" :  23  }, 
+  {  "Value" :  "ON"  ,  "Frequency" :  23  }, 
+  {  "Value" :  "Peravia"  ,  "Frequency" :  22  }, 
+  {  "Value" :  "Santiago"  ,  "Frequency" :  22  }, 
+  {  "Value" :  "NV"  ,  "Frequency" :  21  }, 
+  {  "Value" :  "BC"  ,  "Frequency" :  20  }, 
+  {  "Value" :  "La Habana"  ,  "Frequency" :  20  }, 
+  {  "Value" :  "Anzoategui"  ,  "Frequency" :  19  }, 
+  {  "Value" :  "AR"  ,  "Frequency" :  19  }, 
+  {  "Value" :  "Aragua"  ,  "Frequency" :  19  }, 
+  {  "Value" :  "NE"  ,  "Frequency" :  17  }, 
+  {  "Value" :  "Bolivar"  ,  "Frequency" :  16  }
+]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 
+  {  "x" :  "CA"  ,  "Freq" :  826  }, 
+  {  "x" :  "TX"  ,  "Freq" :  293  }, 
+  {  "x" :  "FL"  ,  "Freq" :  260  }, 
+  {  "x" :  "NY"  ,  "Freq" :  155  }, 
+  {  "x" :  "IL"  ,  "Freq" :  154  }, 
+  {  "x" :  "OH"  ,  "Freq" :  150  }, 
+  {  "x" :  "PA"  ,  "Freq" :  124  }, 
+  {  "x" :  "GA"  ,  "Freq" :  115  }, 
+  {  "x" :  "Distrito Nacional"  ,  "Freq" :  92  }, 
+  {  "x" :  "other"  ,  "Freq" :  2284  }
 ]</t>
   </si>
   <si>
@@ -1041,28 +1033,10 @@
 180</t>
   </si>
   <si>
-    <t xml:space="preserve">measurement {{ quantity :: number }}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">number:quantity:measurement</t>
+    <t xml:space="preserve">number</t>
   </si>
   <si>
     <t xml:space="preserve">numeric</t>
-  </si>
-  <si>
-    <t xml:space="preserve">number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{{ write_numeric }}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ready</t>
-  </si>
-  <si>
-    <t xml:space="preserve">215 ;; 190 ;; 235 ;; 190 ;; 200</t>
   </si>
   <si>
     <t xml:space="preserve">[ 
@@ -1338,6 +1312,15 @@
     <t xml:space="preserve">number:quantity:rank</t>
   </si>
   <si>
+    <t xml:space="preserve">yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{ write_numeric }}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ready</t>
+  </si>
+  <si>
     <t xml:space="preserve">75 ;; 75 ;; 74 ;; 74 ;; 75</t>
   </si>
   <si>
@@ -1765,6 +1748,9 @@
 27</t>
   </si>
   <si>
+    <t xml:space="preserve">42 ;; 50 ;; 47 ;; 54 ;; 27</t>
+  </si>
+  <si>
     <t xml:space="preserve">[ 
   {  "STAT" :  "Rows"  ,  "VAL" :  "4,620"  ,  "PER" :  ""  }, 
   {  "STAT" :  "Distinct"  ,  "VAL" :  "149"  ,  "PER" :  "(3.2%)"  }
@@ -2032,9 +2018,6 @@
 21</t>
   </si>
   <si>
-    <t xml:space="preserve">1 ;; 5 ;; 4 ;; 140 ;; 21</t>
-  </si>
-  <si>
     <t xml:space="preserve">[ 
   {  "STAT" :  "Rows"  ,  "VAL" :  "4,620"  ,  "PER" :  ""  }, 
   {  "STAT" :  "Distinct"  ,  "VAL" :  "581"  ,  "PER" :  "(12.6%)"  }, 
@@ -2569,6 +2552,12 @@
 0.243 ;; 
 0.095 ;; 
 0.254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">measurement {{ quantity :: number }}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">number:quantity:measurement</t>
   </si>
   <si>
     <t xml:space="preserve">0 ;; 0 ;; 0.0714285714285714 ;; 0.243226656997048 ;; 0.0952380952380952</t>
@@ -13354,7 +13343,7 @@
         <v>3</v>
       </c>
       <c r="S2" s="6" t="n">
-        <v>0.7572</v>
+        <v>0.865</v>
       </c>
       <c r="T2" s="7" t="s">
         <v>44</v>
@@ -13372,7 +13361,7 @@
         <v>51</v>
       </c>
       <c r="Y2" s="7" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="Z2" s="7" t="s">
         <v>50</v>
@@ -13384,13 +13373,13 @@
         <v>44</v>
       </c>
       <c r="AC2" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AD2" s="7" t="s">
         <v>44</v>
       </c>
       <c r="AE2" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AF2" s="7" t="s">
         <v>44</v>
@@ -13402,16 +13391,16 @@
         <v>44</v>
       </c>
       <c r="AI2" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AJ2" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AK2" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AL2" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AM2" s="7" t="n">
         <v>11</v>
@@ -13426,27 +13415,27 @@
         <v>44</v>
       </c>
       <c r="AQ2" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>44</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="G3" s="10" t="s">
         <v>44</v>
@@ -13467,7 +13456,7 @@
         <v>64</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N3" s="8" t="s">
         <v>44</v>
@@ -13482,10 +13471,10 @@
         <v>44</v>
       </c>
       <c r="R3" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S3" s="6" t="n">
-        <v>0.9714</v>
+        <v>0.4398</v>
       </c>
       <c r="T3" s="7" t="s">
         <v>44</v>
@@ -13500,49 +13489,49 @@
         <v>44</v>
       </c>
       <c r="X3" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y3" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z3" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA3" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB3" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC3" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="AD3" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE3" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="AF3" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG3" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH3" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ3" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="Y3" s="7" t="s">
+      <c r="AK3" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="Z3" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="AA3" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB3" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC3" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD3" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE3" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="AF3" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AG3" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH3" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI3" s="7" t="s">
+      <c r="AL3" s="7" t="s">
         <v>68</v>
-      </c>
-      <c r="AJ3" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="AK3" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="AL3" s="7" t="s">
-        <v>71</v>
       </c>
       <c r="AM3" s="7" t="n">
         <v>14</v>
@@ -13557,21 +13546,21 @@
         <v>44</v>
       </c>
       <c r="AQ3" s="7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>44</v>
@@ -13589,28 +13578,28 @@
         <v>44</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K4" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L4" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="P4" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="Q4" s="8" t="s">
         <v>78</v>
-      </c>
-      <c r="N4" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="O4" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="P4" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q4" s="8" t="s">
-        <v>81</v>
       </c>
       <c r="R4" s="6" t="n">
         <v>4</v>
@@ -13631,49 +13620,49 @@
         <v>44</v>
       </c>
       <c r="X4" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y4" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z4" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA4" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="AB4" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC4" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="Y4" s="7" t="s">
+      <c r="AD4" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE4" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="Z4" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA4" s="7" t="s">
+      <c r="AF4" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG4" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH4" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI4" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="AB4" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC4" s="7" t="s">
+      <c r="AJ4" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="AD4" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE4" s="7" t="s">
+      <c r="AK4" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL4" s="7" t="s">
         <v>86</v>
-      </c>
-      <c r="AF4" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AG4" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH4" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI4" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="AJ4" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="AK4" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AL4" s="7" t="s">
-        <v>89</v>
       </c>
       <c r="AM4" s="7" t="n">
         <v>12</v>
@@ -13688,21 +13677,21 @@
         <v>44</v>
       </c>
       <c r="AQ4" s="7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>44</v>
@@ -13720,28 +13709,28 @@
         <v>44</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="K5" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L5" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="O5" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="P5" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="M5" s="11" t="s">
+      <c r="Q5" s="8" t="s">
         <v>96</v>
-      </c>
-      <c r="N5" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="O5" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="P5" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q5" s="8" t="s">
-        <v>99</v>
       </c>
       <c r="R5" s="6" t="n">
         <v>4</v>
@@ -13753,58 +13742,58 @@
         <v>44</v>
       </c>
       <c r="U5" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="V5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="W5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="X5" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y5" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z5" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="AA5" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="AB5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC5" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="AD5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE5" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="V5" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="W5" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="X5" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="Y5" s="7" t="s">
+      <c r="AF5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI5" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="Z5" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="AA5" s="7" t="s">
+      <c r="AJ5" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="AB5" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC5" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="AD5" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE5" s="7" t="s">
+      <c r="AK5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL5" s="7" t="s">
         <v>103</v>
-      </c>
-      <c r="AF5" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AG5" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH5" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI5" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="AJ5" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="AK5" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AL5" s="7" t="s">
-        <v>106</v>
       </c>
       <c r="AM5" s="7" t="n">
         <v>4</v>
@@ -13819,21 +13808,21 @@
         <v>44</v>
       </c>
       <c r="AQ5" s="7" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>44</v>
@@ -13851,28 +13840,28 @@
         <v>44</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="K6" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L6" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="N6" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="O6" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="P6" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="M6" s="11" t="s">
+      <c r="Q6" s="8" t="s">
         <v>113</v>
-      </c>
-      <c r="N6" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="O6" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="P6" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q6" s="8" t="s">
-        <v>116</v>
       </c>
       <c r="R6" s="6" t="n">
         <v>4</v>
@@ -13884,7 +13873,7 @@
         <v>44</v>
       </c>
       <c r="U6" s="7" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="V6" s="7" t="s">
         <v>44</v>
@@ -13893,49 +13882,49 @@
         <v>44</v>
       </c>
       <c r="X6" s="7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="Y6" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z6" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="AA6" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="AB6" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC6" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="AD6" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE6" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="AF6" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG6" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH6" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI6" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="AJ6" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="AK6" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL6" s="7" t="s">
         <v>117</v>
-      </c>
-      <c r="Z6" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="AA6" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="AB6" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC6" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD6" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE6" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="AF6" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AG6" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH6" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI6" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="AJ6" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="AK6" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AL6" s="7" t="s">
-        <v>120</v>
       </c>
       <c r="AM6" s="7" t="n">
         <v>3</v>
@@ -13950,27 +13939,27 @@
         <v>44</v>
       </c>
       <c r="AQ6" s="7" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="10" t="s">
         <v>122</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>44</v>
       </c>
       <c r="G7" s="10" t="s">
         <v>44</v>
@@ -13982,16 +13971,16 @@
         <v>44</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K7" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>64</v>
+        <v>124</v>
       </c>
       <c r="M7" s="11" t="s">
-        <v>65</v>
+        <v>125</v>
       </c>
       <c r="N7" s="8" t="s">
         <v>44</v>
@@ -14009,7 +13998,7 @@
         <v>3</v>
       </c>
       <c r="S7" s="6" t="n">
-        <v>0.6726</v>
+        <v>0.8314</v>
       </c>
       <c r="T7" s="7" t="s">
         <v>44</v>
@@ -14024,13 +14013,13 @@
         <v>44</v>
       </c>
       <c r="X7" s="7" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="Y7" s="7" t="s">
-        <v>44</v>
+        <v>126</v>
       </c>
       <c r="Z7" s="7" t="s">
-        <v>51</v>
+        <v>125</v>
       </c>
       <c r="AA7" s="7" t="s">
         <v>44</v>
@@ -14039,13 +14028,13 @@
         <v>44</v>
       </c>
       <c r="AC7" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AD7" s="7" t="s">
         <v>44</v>
       </c>
       <c r="AE7" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AF7" s="7" t="s">
         <v>44</v>
@@ -14057,16 +14046,16 @@
         <v>44</v>
       </c>
       <c r="AI7" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AJ7" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AK7" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AL7" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AM7" s="7" t="n">
         <v>22</v>
@@ -14081,27 +14070,27 @@
         <v>44</v>
       </c>
       <c r="AQ7" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>44</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G8" s="10" t="s">
         <v>44</v>
@@ -14113,16 +14102,16 @@
         <v>44</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K8" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>64</v>
+        <v>124</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>65</v>
+        <v>125</v>
       </c>
       <c r="N8" s="8" t="s">
         <v>44</v>
@@ -14140,7 +14129,7 @@
         <v>3</v>
       </c>
       <c r="S8" s="6" t="n">
-        <v>0.9505</v>
+        <v>0.982</v>
       </c>
       <c r="T8" s="7" t="s">
         <v>44</v>
@@ -14155,13 +14144,13 @@
         <v>44</v>
       </c>
       <c r="X8" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Y8" s="7" t="s">
-        <v>67</v>
+        <v>126</v>
       </c>
       <c r="Z8" s="7" t="s">
-        <v>65</v>
+        <v>125</v>
       </c>
       <c r="AA8" s="7" t="s">
         <v>44</v>
@@ -14170,13 +14159,13 @@
         <v>44</v>
       </c>
       <c r="AC8" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AD8" s="7" t="s">
         <v>44</v>
       </c>
       <c r="AE8" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AF8" s="7" t="s">
         <v>44</v>
@@ -14188,16 +14177,16 @@
         <v>44</v>
       </c>
       <c r="AI8" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AJ8" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK8" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AL8" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AM8" s="7" t="n">
         <v>25</v>
@@ -14212,21 +14201,21 @@
         <v>44</v>
       </c>
       <c r="AQ8" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>44</v>
@@ -14244,13 +14233,13 @@
         <v>44</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K9" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M9" s="11" t="s">
         <v>146</v>
@@ -14268,10 +14257,10 @@
         <v>44</v>
       </c>
       <c r="R9" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S9" s="6" t="n">
-        <v>0.5814</v>
+        <v>0.4289</v>
       </c>
       <c r="T9" s="7" t="s">
         <v>44</v>
@@ -14286,7 +14275,7 @@
         <v>44</v>
       </c>
       <c r="X9" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="Y9" s="7" t="s">
         <v>44</v>
@@ -14295,40 +14284,40 @@
         <v>146</v>
       </c>
       <c r="AA9" s="7" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="AB9" s="7" t="s">
         <v>44</v>
       </c>
       <c r="AC9" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="AD9" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE9" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="AF9" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG9" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH9" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI9" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="AJ9" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="AD9" s="7" t="s">
+      <c r="AK9" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="AE9" s="7" t="s">
+      <c r="AL9" s="7" t="s">
         <v>151</v>
-      </c>
-      <c r="AF9" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="AG9" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH9" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI9" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="AJ9" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="AK9" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="AL9" s="7" t="s">
-        <v>156</v>
       </c>
       <c r="AM9" s="7" t="n">
         <v>3</v>
@@ -14343,21 +14332,21 @@
         <v>44</v>
       </c>
       <c r="AQ9" s="7" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>44</v>
@@ -14375,16 +14364,16 @@
         <v>44</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="K10" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="N10" s="8" t="s">
         <v>44</v>
@@ -14408,7 +14397,7 @@
         <v>44</v>
       </c>
       <c r="U10" s="7" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="V10" s="7" t="s">
         <v>44</v>
@@ -14417,13 +14406,13 @@
         <v>44</v>
       </c>
       <c r="X10" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="Y10" s="7" t="s">
         <v>44</v>
       </c>
       <c r="Z10" s="7" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="AA10" s="7" t="s">
         <v>147</v>
@@ -14432,34 +14421,34 @@
         <v>44</v>
       </c>
       <c r="AC10" s="7" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="AD10" s="7" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AE10" s="7" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="AF10" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="AG10" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH10" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI10" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="AJ10" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="AG10" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH10" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI10" s="7" t="s">
+      <c r="AK10" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="AJ10" s="7" t="s">
+      <c r="AL10" s="7" t="s">
         <v>166</v>
-      </c>
-      <c r="AK10" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="AL10" s="7" t="s">
-        <v>168</v>
       </c>
       <c r="AM10" s="7" t="n">
         <v>2</v>
@@ -14474,27 +14463,27 @@
         <v>44</v>
       </c>
       <c r="AQ10" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" s="5" t="s">
+      <c r="E11" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" s="10" t="s">
         <v>171</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>173</v>
       </c>
       <c r="G11" s="10" t="s">
         <v>44</v>
@@ -14506,16 +14495,16 @@
         <v>44</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="K11" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="N11" s="8" t="s">
         <v>44</v>
@@ -14539,7 +14528,7 @@
         <v>44</v>
       </c>
       <c r="U11" s="7" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="V11" s="7" t="s">
         <v>44</v>
@@ -14548,49 +14537,49 @@
         <v>44</v>
       </c>
       <c r="X11" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Y11" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="Z11" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA11" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB11" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC11" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="AD11" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE11" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="AF11" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG11" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH11" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI11" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="AJ11" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="Z11" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="AA11" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB11" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC11" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD11" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE11" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="AF11" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AG11" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH11" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI11" s="7" t="s">
+      <c r="AK11" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="AJ11" s="7" t="s">
+      <c r="AL11" s="7" t="s">
         <v>179</v>
-      </c>
-      <c r="AK11" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="AL11" s="7" t="s">
-        <v>181</v>
       </c>
       <c r="AM11" s="7" t="n">
         <v>1</v>
@@ -14605,27 +14594,27 @@
         <v>44</v>
       </c>
       <c r="AQ11" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="5" t="s">
+      <c r="E12" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F12" s="10" t="s">
         <v>184</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>186</v>
       </c>
       <c r="G12" s="10" t="s">
         <v>44</v>
@@ -14637,16 +14626,16 @@
         <v>44</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K12" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L12" s="10" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="N12" s="8" t="s">
         <v>44</v>
@@ -14670,7 +14659,7 @@
         <v>44</v>
       </c>
       <c r="U12" s="7" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="V12" s="7" t="s">
         <v>44</v>
@@ -14679,13 +14668,13 @@
         <v>44</v>
       </c>
       <c r="X12" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Y12" s="7" t="s">
         <v>44</v>
       </c>
       <c r="Z12" s="7" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AA12" s="7" t="s">
         <v>44</v>
@@ -14694,13 +14683,13 @@
         <v>44</v>
       </c>
       <c r="AC12" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AD12" s="7" t="s">
         <v>44</v>
       </c>
       <c r="AE12" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AF12" s="7" t="s">
         <v>44</v>
@@ -14712,16 +14701,16 @@
         <v>44</v>
       </c>
       <c r="AI12" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="AJ12" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="AK12" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="AJ12" s="7" t="s">
+      <c r="AL12" s="7" t="s">
         <v>189</v>
-      </c>
-      <c r="AK12" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="AL12" s="7" t="s">
-        <v>191</v>
       </c>
       <c r="AM12" s="7" t="n">
         <v>1</v>
@@ -14736,21 +14725,21 @@
         <v>44</v>
       </c>
       <c r="AQ12" s="7" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>193</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>195</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>44</v>
@@ -14768,28 +14757,28 @@
         <v>44</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="K13" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L13" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="N13" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="O13" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="P13" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="M13" s="11" t="s">
+      <c r="Q13" s="8" t="s">
         <v>78</v>
-      </c>
-      <c r="N13" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="O13" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="P13" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q13" s="8" t="s">
-        <v>81</v>
       </c>
       <c r="R13" s="6" t="n">
         <v>4</v>
@@ -14810,49 +14799,49 @@
         <v>44</v>
       </c>
       <c r="X13" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y13" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z13" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA13" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="AB13" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC13" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="Y13" s="7" t="s">
+      <c r="AD13" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE13" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="Z13" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA13" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="AB13" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC13" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="AD13" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE13" s="7" t="s">
+      <c r="AF13" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG13" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH13" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI13" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="AJ13" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK13" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL13" s="7" t="s">
         <v>86</v>
-      </c>
-      <c r="AF13" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AG13" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH13" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI13" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="AJ13" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="AK13" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AL13" s="7" t="s">
-        <v>89</v>
       </c>
       <c r="AM13" s="7" t="n">
         <v>10</v>
@@ -14867,21 +14856,21 @@
         <v>44</v>
       </c>
       <c r="AQ13" s="7" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="14" ht="25" customHeight="1">
       <c r="A14" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>200</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>202</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>44</v>
@@ -14899,28 +14888,28 @@
         <v>44</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="K14" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L14" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="N14" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="O14" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="P14" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="M14" s="11" t="s">
+      <c r="Q14" s="8" t="s">
         <v>78</v>
-      </c>
-      <c r="N14" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="O14" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="P14" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q14" s="8" t="s">
-        <v>81</v>
       </c>
       <c r="R14" s="6" t="n">
         <v>4</v>
@@ -14941,49 +14930,49 @@
         <v>44</v>
       </c>
       <c r="X14" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y14" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z14" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA14" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="AB14" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC14" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="Y14" s="7" t="s">
+      <c r="AD14" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE14" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="Z14" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA14" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="AB14" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC14" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="AD14" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE14" s="7" t="s">
+      <c r="AF14" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG14" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH14" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI14" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="AJ14" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="AK14" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL14" s="7" t="s">
         <v>86</v>
-      </c>
-      <c r="AF14" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AG14" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH14" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI14" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="AJ14" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="AK14" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AL14" s="7" t="s">
-        <v>89</v>
       </c>
       <c r="AM14" s="7" t="n">
         <v>10</v>
@@ -14998,21 +14987,21 @@
         <v>44</v>
       </c>
       <c r="AQ14" s="7" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="15" ht="25" customHeight="1">
       <c r="A15" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>207</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>209</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>44</v>
@@ -15030,16 +15019,16 @@
         <v>44</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K15" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="M15" s="11" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="N15" s="8" t="s">
         <v>44</v>
@@ -15054,10 +15043,10 @@
         <v>44</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S15" s="6" t="n">
-        <v>0.4659</v>
+        <v>0.6255</v>
       </c>
       <c r="T15" s="7" t="s">
         <v>44</v>
@@ -15072,31 +15061,31 @@
         <v>44</v>
       </c>
       <c r="X15" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="Y15" s="7" t="s">
         <v>44</v>
       </c>
       <c r="Z15" s="7" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="AA15" s="7" t="s">
-        <v>44</v>
+        <v>147</v>
       </c>
       <c r="AB15" s="7" t="s">
         <v>44</v>
       </c>
       <c r="AC15" s="7" t="s">
-        <v>52</v>
+        <v>159</v>
       </c>
       <c r="AD15" s="7" t="s">
-        <v>44</v>
+        <v>160</v>
       </c>
       <c r="AE15" s="7" t="s">
-        <v>53</v>
+        <v>161</v>
       </c>
       <c r="AF15" s="7" t="s">
-        <v>44</v>
+        <v>209</v>
       </c>
       <c r="AG15" s="7" t="s">
         <v>44</v>
@@ -15105,16 +15094,16 @@
         <v>44</v>
       </c>
       <c r="AI15" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="AJ15" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="AJ15" s="7" t="s">
+      <c r="AK15" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="AK15" s="7" t="s">
+      <c r="AL15" s="7" t="s">
         <v>213</v>
-      </c>
-      <c r="AL15" s="7" t="s">
-        <v>214</v>
       </c>
       <c r="AM15" s="7" t="n">
         <v>3</v>
@@ -15129,21 +15118,21 @@
         <v>44</v>
       </c>
       <c r="AQ15" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="16" ht="25" customHeight="1">
       <c r="A16" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="5" t="s">
+      <c r="D16" s="5" t="s">
         <v>217</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>218</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>44</v>
@@ -15161,13 +15150,13 @@
         <v>44</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K16" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L16" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M16" s="11" t="s">
         <v>146</v>
@@ -15185,10 +15174,10 @@
         <v>44</v>
       </c>
       <c r="R16" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S16" s="6" t="n">
-        <v>0.542</v>
+        <v>0.3866</v>
       </c>
       <c r="T16" s="7" t="s">
         <v>44</v>
@@ -15203,7 +15192,7 @@
         <v>44</v>
       </c>
       <c r="X16" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="Y16" s="7" t="s">
         <v>44</v>
@@ -15212,40 +15201,40 @@
         <v>146</v>
       </c>
       <c r="AA16" s="7" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="AB16" s="7" t="s">
         <v>44</v>
       </c>
       <c r="AC16" s="7" t="s">
-        <v>149</v>
+        <v>53</v>
       </c>
       <c r="AD16" s="7" t="s">
-        <v>150</v>
+        <v>44</v>
       </c>
       <c r="AE16" s="7" t="s">
-        <v>151</v>
+        <v>54</v>
       </c>
       <c r="AF16" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG16" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH16" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI16" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="AJ16" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="AG16" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH16" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI16" s="7" t="s">
+      <c r="AK16" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="AJ16" s="7" t="s">
+      <c r="AL16" s="7" t="s">
         <v>222</v>
-      </c>
-      <c r="AK16" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="AL16" s="7" t="s">
-        <v>224</v>
       </c>
       <c r="AM16" s="7" t="n">
         <v>3</v>
@@ -15260,21 +15249,21 @@
         <v>44</v>
       </c>
       <c r="AQ16" s="7" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17" ht="25" customHeight="1">
       <c r="A17" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>226</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>228</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>44</v>
@@ -15292,16 +15281,16 @@
         <v>44</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="K17" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>44</v>
+        <v>146</v>
       </c>
       <c r="M17" s="11" t="s">
-        <v>44</v>
+        <v>146</v>
       </c>
       <c r="N17" s="8" t="s">
         <v>44</v>
@@ -15316,10 +15305,10 @@
         <v>44</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" s="6" t="n">
-        <v>0.2434</v>
+        <v>0.3096</v>
       </c>
       <c r="T17" s="7" t="s">
         <v>44</v>
@@ -15334,13 +15323,13 @@
         <v>44</v>
       </c>
       <c r="X17" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="Y17" s="7" t="s">
         <v>44</v>
       </c>
       <c r="Z17" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AA17" s="7" t="s">
         <v>44</v>
@@ -15349,13 +15338,13 @@
         <v>44</v>
       </c>
       <c r="AC17" s="7" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="AD17" s="7" t="s">
         <v>44</v>
       </c>
       <c r="AE17" s="7" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="AF17" s="7" t="s">
         <v>44</v>
@@ -15367,16 +15356,16 @@
         <v>44</v>
       </c>
       <c r="AI17" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="AJ17" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="AK17" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="AJ17" s="7" t="s">
+      <c r="AL17" s="7" t="s">
         <v>231</v>
-      </c>
-      <c r="AK17" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="AL17" s="7" t="s">
-        <v>233</v>
       </c>
       <c r="AM17" s="7" t="n">
         <v>3</v>
@@ -15391,21 +15380,21 @@
         <v>44</v>
       </c>
       <c r="AQ17" s="7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="18" ht="25" customHeight="1">
       <c r="A18" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>235</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>237</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>44</v>
@@ -15423,16 +15412,16 @@
         <v>44</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="K18" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>145</v>
+        <v>237</v>
       </c>
       <c r="M18" s="11" t="s">
-        <v>146</v>
+        <v>238</v>
       </c>
       <c r="N18" s="8" t="s">
         <v>44</v>
@@ -15450,7 +15439,7 @@
         <v>3</v>
       </c>
       <c r="S18" s="6" t="n">
-        <v>0.6077</v>
+        <v>0.7303</v>
       </c>
       <c r="T18" s="7" t="s">
         <v>44</v>
@@ -15465,13 +15454,13 @@
         <v>44</v>
       </c>
       <c r="X18" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="Y18" s="7" t="s">
         <v>44</v>
       </c>
       <c r="Z18" s="7" t="s">
-        <v>146</v>
+        <v>238</v>
       </c>
       <c r="AA18" s="7" t="s">
         <v>147</v>
@@ -15480,13 +15469,13 @@
         <v>44</v>
       </c>
       <c r="AC18" s="7" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="AD18" s="7" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AE18" s="7" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="AF18" s="7" t="s">
         <v>239</v>
@@ -15560,10 +15549,10 @@
         <v>0</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>145</v>
+        <v>237</v>
       </c>
       <c r="M19" s="11" t="s">
-        <v>146</v>
+        <v>238</v>
       </c>
       <c r="N19" s="8" t="s">
         <v>44</v>
@@ -15581,7 +15570,7 @@
         <v>3</v>
       </c>
       <c r="S19" s="6" t="n">
-        <v>0.6492</v>
+        <v>0.5969</v>
       </c>
       <c r="T19" s="7" t="s">
         <v>44</v>
@@ -15596,13 +15585,13 @@
         <v>44</v>
       </c>
       <c r="X19" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="Y19" s="7" t="s">
         <v>44</v>
       </c>
       <c r="Z19" s="7" t="s">
-        <v>146</v>
+        <v>238</v>
       </c>
       <c r="AA19" s="7" t="s">
         <v>147</v>
@@ -15611,13 +15600,13 @@
         <v>44</v>
       </c>
       <c r="AC19" s="7" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="AD19" s="7" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AE19" s="7" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="AF19" s="7" t="s">
         <v>249</v>
@@ -15703,7 +15692,7 @@
         <v>44</v>
       </c>
       <c r="P20" s="8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="Q20" s="8" t="s">
         <v>44</v>
@@ -15727,7 +15716,7 @@
         <v>44</v>
       </c>
       <c r="X20" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="Y20" s="7" t="s">
         <v>44</v>
@@ -15742,13 +15731,13 @@
         <v>44</v>
       </c>
       <c r="AC20" s="7" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="AD20" s="7" t="s">
         <v>261</v>
       </c>
       <c r="AE20" s="7" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="AF20" s="7" t="s">
         <v>262</v>
@@ -15817,7 +15806,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
         <v>37</v>
@@ -15834,7 +15823,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s">
         <v>37</v>
@@ -15851,7 +15840,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B4" t="s">
         <v>37</v>
@@ -15868,7 +15857,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B5" t="s">
         <v>37</v>
@@ -15885,7 +15874,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B6" t="s">
         <v>37</v>
@@ -15902,7 +15891,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B7" t="s">
         <v>37</v>
@@ -15919,7 +15908,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B8" t="s">
         <v>37</v>
@@ -15936,7 +15925,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B9" t="s">
         <v>37</v>
@@ -15953,7 +15942,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B10" t="s">
         <v>37</v>
@@ -15970,7 +15959,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B11" t="s">
         <v>37</v>
@@ -15987,7 +15976,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B12" t="s">
         <v>37</v>
@@ -16004,7 +15993,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B13" t="s">
         <v>37</v>
@@ -16021,7 +16010,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B14" t="s">
         <v>37</v>
@@ -16038,7 +16027,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B15" t="s">
         <v>37</v>
@@ -16055,7 +16044,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B16" t="s">
         <v>37</v>
@@ -16072,7 +16061,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B17" t="s">
         <v>37</v>
@@ -16089,7 +16078,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B18" t="s">
         <v>37</v>
@@ -16106,7 +16095,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B19" t="s">
         <v>37</v>
@@ -16123,7 +16112,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B20" t="s">
         <v>37</v>
@@ -16140,7 +16129,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B21" t="s">
         <v>37</v>
@@ -16157,7 +16146,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B22" t="s">
         <v>37</v>
@@ -16174,7 +16163,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B23" t="s">
         <v>37</v>
@@ -16191,7 +16180,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B24" t="s">
         <v>37</v>
@@ -16208,7 +16197,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B25" t="s">
         <v>37</v>
@@ -16225,7 +16214,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B26" t="s">
         <v>37</v>
@@ -16242,7 +16231,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B27" t="s">
         <v>37</v>
@@ -16259,7 +16248,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B28" t="s">
         <v>37</v>
@@ -16276,7 +16265,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B29" t="s">
         <v>37</v>
@@ -16293,7 +16282,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B30" t="s">
         <v>37</v>
@@ -16310,7 +16299,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B31" t="s">
         <v>37</v>
@@ -16327,7 +16316,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B32" t="s">
         <v>37</v>
@@ -16344,7 +16333,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B33" t="s">
         <v>37</v>

--- a/working-example/baseball/DGF.xlsx
+++ b/working-example/baseball/DGF.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="302">
   <si>
     <t xml:space="preserve">var_name</t>
   </si>
@@ -173,9 +173,6 @@
   </si>
   <si>
     <t xml:space="preserve">text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">name.person</t>
   </si>
   <si>
     <t xml:space="preserve">no</t>
@@ -320,6 +317,60 @@
     <t xml:space="preserve">Player's last name</t>
   </si>
   <si>
+    <t xml:space="preserve">[ 
+  {  "level" :  "Johnson"  ,  "label" :  "Johnson"  }, 
+  {  "level" :  "Perez"  ,  "label" :  "Perez"  }, 
+  {  "level" :  "Martinez"  ,  "label" :  "Martinez"  }, 
+  {  "level" :  "Jones"  ,  "label" :  "Jones"  }, 
+  {  "level" :  "Davis"  ,  "label" :  "Davis"  }, 
+  {  "level" :  "Wilson"  ,  "label" :  "Wilson"  }, 
+  {  "level" :  "Hernandez"  ,  "label" :  "Hernandez"  }, 
+  {  "level" :  "Rodriguez"  ,  "label" :  "Rodriguez"  }, 
+  {  "level" :  "Smith"  ,  "label" :  "Smith"  }, 
+  {  "level" :  "Williams"  ,  "label" :  "Williams"  }, 
+  {  "level" :  "Gonzalez"  ,  "label" :  "Gonzalez"  }, 
+  {  "level" :  "Ramirez"  ,  "label" :  "Ramirez"  }, 
+  {  "level" :  "Young"  ,  "label" :  "Young"  }, 
+  {  "level" :  "Anderson"  ,  "label" :  "Anderson"  }, 
+  {  "level" :  "Brown"  ,  "label" :  "Brown"  }, 
+  {  "level" :  "Miller"  ,  "label" :  "Miller"  }, 
+  {  "level" :  "Garcia"  ,  "label" :  "Garcia"  }, 
+  {  "level" :  "Sanchez"  ,  "label" :  "Sanchez"  }, 
+  {  "level" :  "Castillo"  ,  "label" :  "Castillo"  }, 
+  {  "level" :  "Cruz"  ,  "label" :  "Cruz"  }, 
+  {  "level" :  "Jackson"  ,  "label" :  "Jackson"  }, 
+  {  "level" :  "Lopez"  ,  "label" :  "Lopez"  }, 
+  {  "level" :  "Thompson"  ,  "label" :  "Thompson"  }, 
+  {  "level" :  "Walker"  ,  "label" :  "Walker"  }, 
+  {  "level" :  "Pena"  ,  "label" :  "Pena"  }, 
+  {  "level" :  "Bell"  ,  "label" :  "Bell"  }, 
+  {  "level" :  "Cabrera"  ,  "label" :  "Cabrera"  }, 
+  {  "level" :  "Clark"  ,  "label" :  "Clark"  }, 
+  {  "level" :  "Hill"  ,  "label" :  "Hill"  }, 
+  {  "level" :  "Reed"  ,  "label" :  "Reed"  }, 
+  {  "level" :  "Diaz"  ,  "label" :  "Diaz"  }, 
+  {  "level" :  "Harris"  ,  "label" :  "Harris"  }, 
+  {  "level" :  "Moore"  ,  "label" :  "Moore"  }, 
+  {  "level" :  "Ortiz"  ,  "label" :  "Ortiz"  }, 
+  {  "level" :  "Rivera"  ,  "label" :  "Rivera"  }, 
+  {  "level" :  "White"  ,  "label" :  "White"  }, 
+  {  "level" :  "Wright"  ,  "label" :  "Wright"  }, 
+  {  "level" :  "Alvarez"  ,  "label" :  "Alvarez"  }, 
+  {  "level" :  "Green"  ,  "label" :  "Green"  }, 
+  {  "level" :  "Lee"  ,  "label" :  "Lee"  }, 
+  {  "level" :  "Murphy"  ,  "label" :  "Murphy"  }, 
+  {  "level" :  "Wood"  ,  "label" :  "Wood"  }, 
+  {  "level" :  "Adams"  ,  "label" :  "Adams"  }, 
+  {  "level" :  "Hall"  ,  "label" :  "Hall"  }, 
+  {  "level" :  "Lewis"  ,  "label" :  "Lewis"  }, 
+  {  "level" :  "Morris"  ,  "label" :  "Morris"  }, 
+  {  "level" :  "Myers"  ,  "label" :  "Myers"  }, 
+  {  "level" :  "Patterson"  ,  "label" :  "Patterson"  }, 
+  {  "level" :  "Powell"  ,  "label" :  "Powell"  }, 
+  {  "level" :  "Reyes"  ,  "label" :  "Reyes"  }
+]</t>
+  </si>
+  <si>
     <t xml:space="preserve">Aardsma ;; 
 Aase ;; 
 Abad ;; 
@@ -327,7 +378,16 @@
 Abercrombie</t>
   </si>
   <si>
+    <t xml:space="preserve">geographic {{ mutually_exclusive :: categorical }}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">categorical:mutually_exclusive:geographic</t>
+  </si>
+  <si>
     <t xml:space="preserve">categorical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mutually_exclusive.geographic</t>
   </si>
   <si>
     <t xml:space="preserve">[ 
@@ -339,118 +399,82 @@
     <t xml:space="preserve">Johnson ;; Perez ;; Martinez ;; Jones ;; Davis ;; Wilson ;; Hernandez ;; Rodriguez ;; Smith ;; Williams ;; Gonzalez ;; Ramirez ;; Young ;; Anderson ;; Brown ;; Miller ;; Garcia ;; Sanchez ;; Castillo ;; Cruz ;; Jackson ;; Lopez ;; Thompson ;; Walker ;; Pena ;; Bell ;; Cabrera ;; Clark ;; Hill ;; Reed ;; Diaz ;; Harris ;; Moore ;; Ortiz ;; Rivera ;; White ;; Wright ;; Alvarez ;; Green ;; Lee ;; Mur</t>
   </si>
   <si>
-    <t xml:space="preserve">{
-  "STATS": [
-    {
-      "STAT": "Minimum",
-      "CHARACTERS": 2,
-      "WORDS": 1
-    },
-    {
-      "STAT": "Median",
-      "CHARACTERS": 6,
-      "WORDS": 1
-    },
-    {
-      "STAT": "Mean",
-      "CHARACTERS": 6.49,
-      "WORDS": 1.01
-    },
-    {
-      "STAT": "Max",
-      "CHARACTERS": 14,
-      "WORDS": 3
-    },
-    {
-      "STAT": "Skew",
-      "CHARACTERS": 0.5,
-      "WORDS": 17.05
-    }
-  ],
-  "HIST": [
-    "&lt;?xml version=\"1.0\" encoding=\"UTF-8\"?&gt;\n&lt;svg xmlns=\"http://www.w3.org/2000/svg\" xmlns:xlink=\"http://www.w3.org/1999/xlink\" width=\"48.00pt\" height=\"12.00pt\" viewBox=\"0 0 48.00 12.00\"&gt;\n  &lt;g class=\"svglite\"&gt;\n    &lt;defs&gt;\n      &lt;style type=\"text/css\"&gt;&lt;![CDATA[\n    .svglite line, .svglite polyline, .svglite polygon, .svglite path, .svglite rect, .svglite circle {\n      fill: none;\n      stroke: #000000;\n      stroke-linecap: round;\n      stroke-linejoin: round;\n      stroke-miterlimit: 10.00;\n    }\n    .svglite text {\n      white-space: pre;\n    }\n    .svglite g.glyphgroup path {\n      fill: inherit;\n      stroke: none;\n    }\n  ]]&gt;&lt;\/style&gt;\n    &lt;\/defs&gt;\n    &lt;rect width=\"100%\" height=\"100%\" style=\"stroke: none; fill: none;\"/&gt;\n    &lt;defs&gt;\n      &lt;clipPath id=\"cpMC4wMHw0OC4wMHwwLjAwfDEyLjAw\"&gt;\n        &lt;rect x=\"0.00\" y=\"0.00\" width=\"48.00\" height=\"12.00\"/&gt;\n      &lt;\/clipPath&gt;\n    &lt;\/defs&gt;\n    &lt;g clip-path=\"url(#cpMC4wMHw0OC4wMHwwLjAwfDEyLjAw)\"&gt;\n&lt;\/g&gt;\n    &lt;defs&gt;\n      &lt;clipPath id=\"cpMC4wMHw0OC4wMHwyLjg4fDEyLjAw\"&gt;\n        &lt;rect x=\"0.00\" y=\"2.88\" width=\"48.00\" height=\"9.12\"/&gt;\n      &lt;\/clipPath&gt;\n    &lt;\/defs&gt;\n    &lt;g clip-path=\"url(#cpMC4wMHw0OC4wMHwyLjg4fDEyLjAw)\"&gt;\n      &lt;rect x=\"1.78\" y=\"11.22\" width=\"3.70\" height=\"0.44\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"5.48\" y=\"8.63\" width=\"3.70\" height=\"3.03\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"9.19\" y=\"5.07\" width=\"3.70\" height=\"6.59\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"12.89\" y=\"3.22\" width=\"3.70\" height=\"8.44\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"16.59\" y=\"4.64\" width=\"3.70\" height=\"7.03\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"20.30\" y=\"6.82\" width=\"3.70\" height=\"4.84\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"24.00\" y=\"9.18\" width=\"3.70\" height=\"2.48\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"27.70\" y=\"10.78\" width=\"3.70\" height=\"0.88\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"31.41\" y=\"11.22\" width=\"3.70\" height=\"0.45\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"35.11\" y=\"11.59\" width=\"3.70\" height=\"0.074\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"38.81\" y=\"11.62\" width=\"3.70\" height=\"0.045\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"42.52\" y=\"11.65\" width=\"3.70\" height=\"0.015\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n    &lt;\/g&gt;\n  &lt;\/g&gt;\n&lt;\/svg&gt;\n",
-    "&lt;?xml version=\"1.0\" encoding=\"UTF-8\"?&gt;\n&lt;svg xmlns=\"http://www.w3.org/2000/svg\" xmlns:xlink=\"http://www.w3.org/1999/xlink\" width=\"48.00pt\" height=\"12.00pt\" viewBox=\"0 0 48.00 12.00\"&gt;\n  &lt;g class=\"svglite\"&gt;\n    &lt;defs&gt;\n      &lt;style type=\"text/css\"&gt;&lt;![CDATA[\n    .svglite line, .svglite polyline, .svglite polygon, .svglite path, .svglite rect, .svglite circle {\n      fill: none;\n      stroke: #000000;\n      stroke-linecap: round;\n      stroke-linejoin: round;\n      stroke-miterlimit: 10.00;\n    }\n    .svglite text {\n      white-space: pre;\n    }\n    .svglite g.glyphgroup path {\n      fill: inherit;\n      stroke: none;\n    }\n  ]]&gt;&lt;\/style&gt;\n    &lt;\/defs&gt;\n    &lt;rect width=\"100%\" height=\"100%\" style=\"stroke: none; fill: none;\"/&gt;\n    &lt;defs&gt;\n      &lt;clipPath id=\"cpMC4wMHw0OC4wMHwwLjAwfDEyLjAw\"&gt;\n        &lt;rect x=\"0.00\" y=\"0.00\" width=\"48.00\" height=\"12.00\"/&gt;\n      &lt;\/clipPath&gt;\n    &lt;\/defs&gt;\n    &lt;g clip-path=\"url(#cpMC4wMHw0OC4wMHwwLjAwfDEyLjAw)\"&gt;\n&lt;\/g&gt;\n    &lt;defs&gt;\n      &lt;clipPath id=\"cpMC4wMHw0OC4wMHwyLjg4fDEyLjAw\"&gt;\n        &lt;rect x=\"0.00\" y=\"2.88\" width=\"48.00\" height=\"9.12\"/&gt;\n      &lt;\/clipPath&gt;\n    &lt;\/defs&gt;\n    &lt;g clip-path=\"url(#cpMC4wMHw0OC4wMHwyLjg4fDEyLjAw)\"&gt;\n      &lt;rect x=\"1.78\" y=\"3.22\" width=\"4.44\" height=\"8.44\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"6.22\" y=\"11.66\" width=\"4.44\" height=\"0.00\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"10.67\" y=\"11.66\" width=\"4.44\" height=\"0.00\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"15.11\" y=\"11.66\" width=\"4.44\" height=\"0.00\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"19.56\" y=\"11.63\" width=\"4.44\" height=\"0.033\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"24.00\" y=\"11.66\" width=\"4.44\" height=\"0.00\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"28.44\" y=\"11.66\" width=\"4.44\" height=\"0.00\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"32.89\" y=\"11.66\" width=\"4.44\" height=\"0.00\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"37.33\" y=\"11.66\" width=\"4.44\" height=\"0.00\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"41.78\" y=\"11.65\" width=\"4.44\" height=\"0.0073\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n    &lt;\/g&gt;\n  &lt;\/g&gt;\n&lt;\/svg&gt;\n"
-  ],
-  "COMMON": [
-    {
-      "Value": "Johnson",
-      "Frequency": 28
-    },
-    {
-      "Value": "Perez",
-      "Frequency": 28
-    },
-    {
-      "Value": "Martinez",
-      "Frequency": 26
-    },
-    {
-      "Value": "Jones",
-      "Frequency": 25
-    },
-    {
-      "Value": "Davis",
-      "Frequency": 24
-    },
-    {
-      "Value": "Wilson",
-      "Frequency": 24
-    }
-  ]
-}</t>
-  </si>
-  <si>
     <t xml:space="preserve">[ 
-  {  "ww" :  "Johnson"  ,  "Freq" :  28  }, 
-  {  "ww" :  "Perez"  ,  "Freq" :  28  }, 
-  {  "ww" :  "Martinez"  ,  "Freq" :  26  }, 
-  {  "ww" :  "Jones"  ,  "Freq" :  25  }, 
-  {  "ww" :  "Davis"  ,  "Freq" :  24  }, 
-  {  "ww" :  "Wilson"  ,  "Freq" :  24  }, 
-  {  "ww" :  "Hernandez"  ,  "Freq" :  21  }, 
-  {  "ww" :  "Rodriguez"  ,  "Freq" :  19  }, 
-  {  "ww" :  "Smith"  ,  "Freq" :  19  }, 
-  {  "ww" :  "Williams"  ,  "Freq" :  19  }, 
-  {  "ww" :  "Gonzalez"  ,  "Freq" :  18  }, 
-  {  "ww" :  "Ramirez"  ,  "Freq" :  18  }, 
-  {  "ww" :  "Young"  ,  "Freq" :  17  }, 
-  {  "ww" :  "Anderson"  ,  "Freq" :  16  }, 
-  {  "ww" :  "Brown"  ,  "Freq" :  16  }, 
-  {  "ww" :  "Miller"  ,  "Freq" :  16  }, 
-  {  "ww" :  "Garcia"  ,  "Freq" :  15  }, 
-  {  "ww" :  "Sanchez"  ,  "Freq" :  14  }, 
-  {  "ww" :  "Castillo"  ,  "Freq" :  12  }, 
-  {  "ww" :  "Cruz"  ,  "Freq" :  12  }, 
-  {  "ww" :  "Jackson"  ,  "Freq" :  12  }, 
-  {  "ww" :  "Lopez"  ,  "Freq" :  12  }, 
-  {  "ww" :  "Thompson"  ,  "Freq" :  12  }, 
-  {  "ww" :  "Walker"  ,  "Freq" :  12  }, 
-  {  "ww" :  "Pena"  ,  "Freq" :  11  }, 
-  {  "ww" :  "Bell"  ,  "Freq" :  10  }, 
-  {  "ww" :  "Cabrera"  ,  "Freq" :  10  }, 
-  {  "ww" :  "Clark"  ,  "Freq" :  10  }, 
-  {  "ww" :  "Hill"  ,  "Freq" :  10  }, 
-  {  "ww" :  "Reed"  ,  "Freq" :  10  }, 
-  {  "ww" :  "Diaz"  ,  "Freq" :  9  }, 
-  {  "ww" :  "Harris"  ,  "Freq" :  9  }, 
-  {  "ww" :  "Moore"  ,  "Freq" :  9  }, 
-  {  "ww" :  "Ortiz"  ,  "Freq" :  9  }, 
-  {  "ww" :  "Rivera"  ,  "Freq" :  9  }, 
-  {  "ww" :  "White"  ,  "Freq" :  9  }, 
-  {  "ww" :  "Wright"  ,  "Freq" :  9  }, 
-  {  "ww" :  "Alvarez"  ,  "Freq" :  8  }, 
-  {  "ww" :  "Green"  ,  "Freq" :  8  }, 
-  {  "ww" :  "Lee"  ,  "Freq" :  8  }, 
-  {  "ww" :  "Murphy"  ,  "Freq" :  8  }, 
-  {  "ww" :  "Wood"  ,  "Freq" :  8  }, 
-  {  "ww" :  "Adams"  ,  "Freq" :  7  }, 
-  {  "ww" :  "Hall"  ,  "Freq" :  7  }, 
-  {  "ww" :  "Lewis"  ,  "Freq" :  7  }, 
-  {  "ww" :  "Morris"  ,  "Freq" :  7  }, 
-  {  "ww" :  "Myers"  ,  "Freq" :  7  }, 
-  {  "ww" :  "Patterson"  ,  "Freq" :  7  }, 
-  {  "ww" :  "Powell"  ,  "Freq" :  7  }, 
-  {  "ww" :  "Reyes"  ,  "Freq" :  7  }
+  {  "Value" :  "Johnson"  ,  "Frequency" :  28  }, 
+  {  "Value" :  "Perez"  ,  "Frequency" :  28  }, 
+  {  "Value" :  "Martinez"  ,  "Frequency" :  26  }, 
+  {  "Value" :  "Jones"  ,  "Frequency" :  25  }, 
+  {  "Value" :  "Davis"  ,  "Frequency" :  24  }, 
+  {  "Value" :  "Wilson"  ,  "Frequency" :  24  }, 
+  {  "Value" :  "Hernandez"  ,  "Frequency" :  21  }, 
+  {  "Value" :  "Rodriguez"  ,  "Frequency" :  19  }, 
+  {  "Value" :  "Smith"  ,  "Frequency" :  19  }, 
+  {  "Value" :  "Williams"  ,  "Frequency" :  19  }, 
+  {  "Value" :  "Gonzalez"  ,  "Frequency" :  18  }, 
+  {  "Value" :  "Ramirez"  ,  "Frequency" :  18  }, 
+  {  "Value" :  "Young"  ,  "Frequency" :  17  }, 
+  {  "Value" :  "Anderson"  ,  "Frequency" :  16  }, 
+  {  "Value" :  "Brown"  ,  "Frequency" :  16  }, 
+  {  "Value" :  "Miller"  ,  "Frequency" :  16  }, 
+  {  "Value" :  "Garcia"  ,  "Frequency" :  15  }, 
+  {  "Value" :  "Sanchez"  ,  "Frequency" :  14  }, 
+  {  "Value" :  "Castillo"  ,  "Frequency" :  12  }, 
+  {  "Value" :  "Cruz"  ,  "Frequency" :  12  }, 
+  {  "Value" :  "Jackson"  ,  "Frequency" :  12  }, 
+  {  "Value" :  "Lopez"  ,  "Frequency" :  12  }, 
+  {  "Value" :  "Thompson"  ,  "Frequency" :  12  }, 
+  {  "Value" :  "Walker"  ,  "Frequency" :  12  }, 
+  {  "Value" :  "Pena"  ,  "Frequency" :  11  }, 
+  {  "Value" :  "Bell"  ,  "Frequency" :  10  }, 
+  {  "Value" :  "Cabrera"  ,  "Frequency" :  10  }, 
+  {  "Value" :  "Clark"  ,  "Frequency" :  10  }, 
+  {  "Value" :  "Hill"  ,  "Frequency" :  10  }, 
+  {  "Value" :  "Reed"  ,  "Frequency" :  10  }, 
+  {  "Value" :  "Diaz"  ,  "Frequency" :  9  }, 
+  {  "Value" :  "Harris"  ,  "Frequency" :  9  }, 
+  {  "Value" :  "Moore"  ,  "Frequency" :  9  }, 
+  {  "Value" :  "Ortiz"  ,  "Frequency" :  9  }, 
+  {  "Value" :  "Rivera"  ,  "Frequency" :  9  }, 
+  {  "Value" :  "White"  ,  "Frequency" :  9  }, 
+  {  "Value" :  "Wright"  ,  "Frequency" :  9  }, 
+  {  "Value" :  "Alvarez"  ,  "Frequency" :  8  }, 
+  {  "Value" :  "Green"  ,  "Frequency" :  8  }, 
+  {  "Value" :  "Lee"  ,  "Frequency" :  8  }, 
+  {  "Value" :  "Murphy"  ,  "Frequency" :  8  }, 
+  {  "Value" :  "Wood"  ,  "Frequency" :  8  }, 
+  {  "Value" :  "Adams"  ,  "Frequency" :  7  }, 
+  {  "Value" :  "Hall"  ,  "Frequency" :  7  }, 
+  {  "Value" :  "Lewis"  ,  "Frequency" :  7  }, 
+  {  "Value" :  "Morris"  ,  "Frequency" :  7  }, 
+  {  "Value" :  "Myers"  ,  "Frequency" :  7  }, 
+  {  "Value" :  "Patterson"  ,  "Frequency" :  7  }, 
+  {  "Value" :  "Powell"  ,  "Frequency" :  7  }, 
+  {  "Value" :  "Reyes"  ,  "Frequency" :  7  }
+]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 
+  {  "x" :  "Johnson"  ,  "Freq" :  28  }, 
+  {  "x" :  "Perez"  ,  "Freq" :  28  }, 
+  {  "x" :  "Martinez"  ,  "Freq" :  26  }, 
+  {  "x" :  "Jones"  ,  "Freq" :  25  }, 
+  {  "x" :  "Davis"  ,  "Freq" :  24  }, 
+  {  "x" :  "Wilson"  ,  "Freq" :  24  }, 
+  {  "x" :  "Hernandez"  ,  "Freq" :  21  }, 
+  {  "x" :  "Rodriguez"  ,  "Freq" :  19  }, 
+  {  "x" :  "Smith"  ,  "Freq" :  19  }, 
+  {  "x" :  "Williams"  ,  "Freq" :  19  }, 
+  {  "x" :  "Gonzalez"  ,  "Freq" :  18  }, 
+  {  "x" :  "Ramirez"  ,  "Freq" :  18  }, 
+  {  "x" :  "Young"  ,  "Freq" :  17  }, 
+  {  "x" :  "Anderson"  ,  "Freq" :  16  }, 
+  {  "x" :  "Brown"  ,  "Freq" :  16  }, 
+  {  "x" :  "Miller"  ,  "Freq" :  16  }, 
+  {  "x" :  "Garcia"  ,  "Freq" :  15  }, 
+  {  "x" :  "Sanchez"  ,  "Freq" :  14  }, 
+  {  "x" :  "Castillo"  ,  "Freq" :  12  }, 
+  {  "x" :  "Cruz"  ,  "Freq" :  12  }, 
+  {  "x" :  "other"  ,  "Freq" :  4233  }
 ]</t>
   </si>
   <si>
@@ -704,60 +728,6 @@
     <t xml:space="preserve">State or province where the player was born: a two-letter postal code for US states, a region name elsewhere (e.g. La Romana); blank if unknown</t>
   </si>
   <si>
-    <t xml:space="preserve">[ 
-  {  "level" :  "CA"  ,  "label" :  "CA"  }, 
-  {  "level" :  "TX"  ,  "label" :  "TX"  }, 
-  {  "level" :  "FL"  ,  "label" :  "FL"  }, 
-  {  "level" :  "NY"  ,  "label" :  "NY"  }, 
-  {  "level" :  "IL"  ,  "label" :  "IL"  }, 
-  {  "level" :  "OH"  ,  "label" :  "OH"  }, 
-  {  "level" :  "PA"  ,  "label" :  "PA"  }, 
-  {  "level" :  "GA"  ,  "label" :  "GA"  }, 
-  {  "level" :  "Distrito Nacional"  ,  "label" :  "Distrito Nacional"  }, 
-  {  "level" :  "MI"  ,  "label" :  "MI"  }, 
-  {  "level" :  "VA"  ,  "label" :  "VA"  }, 
-  {  "level" :  "LA"  ,  "label" :  "LA"  }, 
-  {  "level" :  "NJ"  ,  "label" :  "NJ"  }, 
-  {  "level" :  "NC"  ,  "label" :  "NC"  }, 
-  {  "level" :  "IN"  ,  "label" :  "IN"  }, 
-  {  "level" :  "MO"  ,  "label" :  "MO"  }, 
-  {  "level" :  "TN"  ,  "label" :  "TN"  }, 
-  {  "level" :  "AL"  ,  "label" :  "AL"  }, 
-  {  "level" :  "WA"  ,  "label" :  "WA"  }, 
-  {  "level" :  "MA"  ,  "label" :  "MA"  }, 
-  {  "level" :  "San Pedro de Macoris"  ,  "label" :  "San Pedro de Macoris"  }, 
-  {  "level" :  "KY"  ,  "label" :  "KY"  }, 
-  {  "level" :  "OK"  ,  "label" :  "OK"  }, 
-  {  "level" :  "MS"  ,  "label" :  "MS"  }, 
-  {  "level" :  "SC"  ,  "label" :  "SC"  }, 
-  {  "level" :  "OR"  ,  "label" :  "OR"  }, 
-  {  "level" :  "MD"  ,  "label" :  "MD"  }, 
-  {  "level" :  "AZ"  ,  "label" :  "AZ"  }, 
-  {  "level" :  "San Cristobal"  ,  "label" :  "San Cristobal"  }, 
-  {  "level" :  "Carabobo"  ,  "label" :  "Carabobo"  }, 
-  {  "level" :  "CT"  ,  "label" :  "CT"  }, 
-  {  "level" :  "MN"  ,  "label" :  "MN"  }, 
-  {  "level" :  "Distrito Federal"  ,  "label" :  "Distrito Federal"  }, 
-  {  "level" :  "IA"  ,  "label" :  "IA"  }, 
-  {  "level" :  "KS"  ,  "label" :  "KS"  }, 
-  {  "level" :  "WI"  ,  "label" :  "WI"  }, 
-  {  "level" :  "Zulia"  ,  "label" :  "Zulia"  }, 
-  {  "level" :  "CO"  ,  "label" :  "CO"  }, 
-  {  "level" :  "HI"  ,  "label" :  "HI"  }, 
-  {  "level" :  "ON"  ,  "label" :  "ON"  }, 
-  {  "level" :  "Peravia"  ,  "label" :  "Peravia"  }, 
-  {  "level" :  "Santiago"  ,  "label" :  "Santiago"  }, 
-  {  "level" :  "NV"  ,  "label" :  "NV"  }, 
-  {  "level" :  "BC"  ,  "label" :  "BC"  }, 
-  {  "level" :  "La Habana"  ,  "label" :  "La Habana"  }, 
-  {  "level" :  "Anzoategui"  ,  "label" :  "Anzoategui"  }, 
-  {  "level" :  "AR"  ,  "label" :  "AR"  }, 
-  {  "level" :  "Aragua"  ,  "label" :  "Aragua"  }, 
-  {  "level" :  "NE"  ,  "label" :  "NE"  }, 
-  {  "level" :  "Bolivar"  ,  "label" :  "Bolivar"  }
-]</t>
-  </si>
-  <si>
     <t xml:space="preserve">CO ;; 
 CA ;; 
 La Romana ;; 
@@ -765,15 +735,6 @@
 MI</t>
   </si>
   <si>
-    <t xml:space="preserve">geographic {{ mutually_exclusive :: categorical }}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">categorical:mutually_exclusive:geographic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mutually_exclusive.geographic</t>
-  </si>
-  <si>
     <t xml:space="preserve">[ 
   {  "STAT" :  "Rows"  ,  "VAL" :  "4,620"  ,  "PER" :  ""  }, 
   {  "STAT" :  "Distinct"  ,  "VAL" :  "210"  ,  "PER" :  "(4.5%)"  }, 
@@ -784,71 +745,118 @@
     <t xml:space="preserve">CA ;; TX ;; FL ;; NY ;; IL ;; OH ;; PA ;; GA ;; Distrito Nacional ;; MI ;; VA ;; LA ;; NJ ;; NC ;; IN ;; MO ;; TN ;; AL ;; WA ;; MA ;; San Pedro de Macoris ;; KY ;; OK ;; MS ;; SC ;; OR ;; MD ;; AZ ;; San Cristobal ;; Carabobo ;; CT ;; MN ;; Distrito Federal ;; IA ;; KS ;; WI ;; Zulia ;; CO ;; HI ;; ON ;; Peravia ;; Santiago ;; NV ;; BC ;; La Habana ;; Anzoategui ;; AR ;; Aragua ;; NE ;; Bolivar</t>
   </si>
   <si>
+    <t xml:space="preserve">{
+  "STATS": [
+    {
+      "STAT": "Minimum",
+      "CHARACTERS": 2,
+      "WORDS": 1
+    },
+    {
+      "STAT": "Median",
+      "CHARACTERS": 2,
+      "WORDS": 1
+    },
+    {
+      "STAT": "Mean",
+      "CHARACTERS": 3.63,
+      "WORDS": 1.12
+    },
+    {
+      "STAT": "Max",
+      "CHARACTERS": 22,
+      "WORDS": 4
+    },
+    {
+      "STAT": "Skew",
+      "CHARACTERS": 2.65,
+      "WORDS": 4.45
+    }
+  ],
+  "HIST": [
+    "&lt;?xml version=\"1.0\" encoding=\"UTF-8\"?&gt;\n&lt;svg xmlns=\"http://www.w3.org/2000/svg\" xmlns:xlink=\"http://www.w3.org/1999/xlink\" width=\"48.00pt\" height=\"12.00pt\" viewBox=\"0 0 48.00 12.00\"&gt;\n  &lt;g class=\"svglite\"&gt;\n    &lt;defs&gt;\n      &lt;style type=\"text/css\"&gt;&lt;![CDATA[\n    .svglite line, .svglite polyline, .svglite polygon, .svglite path, .svglite rect, .svglite circle {\n      fill: none;\n      stroke: #000000;\n      stroke-linecap: round;\n      stroke-linejoin: round;\n      stroke-miterlimit: 10.00;\n    }\n    .svglite text {\n      white-space: pre;\n    }\n    .svglite g.glyphgroup path {\n      fill: inherit;\n      stroke: none;\n    }\n  ]]&gt;&lt;\/style&gt;\n    &lt;\/defs&gt;\n    &lt;rect width=\"100%\" height=\"100%\" style=\"stroke: none; fill: none;\"/&gt;\n    &lt;defs&gt;\n      &lt;clipPath id=\"cpMC4wMHw0OC4wMHwwLjAwfDEyLjAw\"&gt;\n        &lt;rect x=\"0.00\" y=\"0.00\" width=\"48.00\" height=\"12.00\"/&gt;\n      &lt;\/clipPath&gt;\n    &lt;\/defs&gt;\n    &lt;g clip-path=\"url(#cpMC4wMHw0OC4wMHwwLjAwfDEyLjAw)\"&gt;\n&lt;\/g&gt;\n    &lt;defs&gt;\n      &lt;clipPath id=\"cpMC4wMHw0OC4wMHwyLjg4fDEyLjAw\"&gt;\n        &lt;rect x=\"0.00\" y=\"2.88\" width=\"48.00\" height=\"9.12\"/&gt;\n      &lt;\/clipPath&gt;\n    &lt;\/defs&gt;\n    &lt;g clip-path=\"url(#cpMC4wMHw0OC4wMHwyLjg4fDEyLjAw)\"&gt;\n      &lt;rect x=\"1.78\" y=\"3.22\" width=\"4.44\" height=\"8.44\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"6.22\" y=\"11.33\" width=\"4.44\" height=\"0.33\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"10.67\" y=\"11.17\" width=\"4.44\" height=\"0.49\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"15.11\" y=\"11.41\" width=\"4.44\" height=\"0.25\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"19.56\" y=\"11.59\" width=\"4.44\" height=\"0.074\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"24.00\" y=\"11.49\" width=\"4.44\" height=\"0.17\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"28.44\" y=\"11.51\" width=\"4.44\" height=\"0.15\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"32.89\" y=\"11.44\" width=\"4.44\" height=\"0.22\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"37.33\" y=\"11.52\" width=\"4.44\" height=\"0.14\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"41.78\" y=\"11.65\" width=\"4.44\" height=\"0.016\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n    &lt;\/g&gt;\n  &lt;\/g&gt;\n&lt;\/svg&gt;\n",
+    "&lt;?xml version=\"1.0\" encoding=\"UTF-8\"?&gt;\n&lt;svg xmlns=\"http://www.w3.org/2000/svg\" xmlns:xlink=\"http://www.w3.org/1999/xlink\" width=\"48.00pt\" height=\"12.00pt\" viewBox=\"0 0 48.00 12.00\"&gt;\n  &lt;g class=\"svglite\"&gt;\n    &lt;defs&gt;\n      &lt;style type=\"text/css\"&gt;&lt;![CDATA[\n    .svglite line, .svglite polyline, .svglite polygon, .svglite path, .svglite rect, .svglite circle {\n      fill: none;\n      stroke: #000000;\n      stroke-linecap: round;\n      stroke-linejoin: round;\n      stroke-miterlimit: 10.00;\n    }\n    .svglite text {\n      white-space: pre;\n    }\n    .svglite g.glyphgroup path {\n      fill: inherit;\n      stroke: none;\n    }\n  ]]&gt;&lt;\/style&gt;\n    &lt;\/defs&gt;\n    &lt;rect width=\"100%\" height=\"100%\" style=\"stroke: none; fill: none;\"/&gt;\n    &lt;defs&gt;\n      &lt;clipPath id=\"cpMC4wMHw0OC4wMHwwLjAwfDEyLjAw\"&gt;\n        &lt;rect x=\"0.00\" y=\"0.00\" width=\"48.00\" height=\"12.00\"/&gt;\n      &lt;\/clipPath&gt;\n    &lt;\/defs&gt;\n    &lt;g clip-path=\"url(#cpMC4wMHw0OC4wMHwwLjAwfDEyLjAw)\"&gt;\n&lt;\/g&gt;\n    &lt;defs&gt;\n      &lt;clipPath id=\"cpMC4wMHw0OC4wMHwyLjg4fDEyLjAw\"&gt;\n        &lt;rect x=\"0.00\" y=\"2.88\" width=\"48.00\" height=\"9.12\"/&gt;\n      &lt;\/clipPath&gt;\n    &lt;\/defs&gt;\n    &lt;g clip-path=\"url(#cpMC4wMHw0OC4wMHwyLjg4fDEyLjAw)\"&gt;\n      &lt;rect x=\"1.78\" y=\"3.22\" width=\"2.96\" height=\"8.44\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"4.74\" y=\"11.66\" width=\"2.96\" height=\"0.00\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"7.70\" y=\"11.66\" width=\"2.96\" height=\"0.00\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"10.67\" y=\"11.66\" width=\"2.96\" height=\"0.00\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"13.63\" y=\"10.98\" width=\"2.96\" height=\"0.69\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"16.59\" y=\"11.66\" width=\"2.96\" height=\"0.00\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"19.56\" y=\"11.66\" width=\"2.96\" height=\"0.00\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"22.52\" y=\"11.66\" width=\"2.96\" height=\"0.00\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"25.48\" y=\"11.66\" width=\"2.96\" height=\"0.00\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"28.44\" y=\"11.61\" width=\"2.96\" height=\"0.056\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"31.41\" y=\"11.66\" width=\"2.96\" height=\"0.00\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"34.37\" y=\"11.66\" width=\"2.96\" height=\"0.00\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"37.33\" y=\"11.66\" width=\"2.96\" height=\"0.00\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"40.30\" y=\"11.66\" width=\"2.96\" height=\"0.00\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n      &lt;rect x=\"43.26\" y=\"11.54\" width=\"2.96\" height=\"0.12\" style=\"stroke-width: 0.38; fill: #D3D3D3;\"/&gt;\n    &lt;\/g&gt;\n  &lt;\/g&gt;\n&lt;\/svg&gt;\n"
+  ],
+  "COMMON": [
+    {
+      "Value": "CA",
+      "Frequency": 826
+    },
+    {
+      "Value": "TX",
+      "Frequency": 293
+    },
+    {
+      "Value": "FL",
+      "Frequency": 260
+    },
+    {
+      "Value": "NY",
+      "Frequency": 155
+    },
+    {
+      "Value": "IL",
+      "Frequency": 154
+    },
+    {
+      "Value": "OH",
+      "Frequency": 150
+    }
+  ]
+}</t>
+  </si>
+  <si>
     <t xml:space="preserve">[ 
-  {  "Value" :  "CA"  ,  "Frequency" :  826  }, 
-  {  "Value" :  "TX"  ,  "Frequency" :  293  }, 
-  {  "Value" :  "FL"  ,  "Frequency" :  260  }, 
-  {  "Value" :  "NY"  ,  "Frequency" :  155  }, 
-  {  "Value" :  "IL"  ,  "Frequency" :  154  }, 
-  {  "Value" :  "OH"  ,  "Frequency" :  150  }, 
-  {  "Value" :  "PA"  ,  "Frequency" :  124  }, 
-  {  "Value" :  "GA"  ,  "Frequency" :  115  }, 
-  {  "Value" :  "Distrito Nacional"  ,  "Frequency" :  92  }, 
-  {  "Value" :  "MI"  ,  "Frequency" :  88  }, 
-  {  "Value" :  "VA"  ,  "Frequency" :  76  }, 
-  {  "Value" :  "LA"  ,  "Frequency" :  75  }, 
-  {  "Value" :  "NJ"  ,  "Frequency" :  75  }, 
-  {  "Value" :  "NC"  ,  "Frequency" :  71  }, 
-  {  "Value" :  "IN"  ,  "Frequency" :  70  }, 
-  {  "Value" :  "MO"  ,  "Frequency" :  68  }, 
-  {  "Value" :  "TN"  ,  "Frequency" :  62  }, 
-  {  "Value" :  "AL"  ,  "Frequency" :  60  }, 
-  {  "Value" :  "WA"  ,  "Frequency" :  59  }, 
-  {  "Value" :  "MA"  ,  "Frequency" :  58  }, 
-  {  "Value" :  "San Pedro de Macoris"  ,  "Frequency" :  58  }, 
-  {  "Value" :  "KY"  ,  "Frequency" :  57  }, 
-  {  "Value" :  "OK"  ,  "Frequency" :  55  }, 
-  {  "Value" :  "MS"  ,  "Frequency" :  54  }, 
-  {  "Value" :  "SC"  ,  "Frequency" :  48  }, 
-  {  "Value" :  "OR"  ,  "Frequency" :  45  }, 
-  {  "Value" :  "MD"  ,  "Frequency" :  42  }, 
-  {  "Value" :  "AZ"  ,  "Frequency" :  41  }, 
-  {  "Value" :  "San Cristobal"  ,  "Frequency" :  40  }, 
-  {  "Value" :  "Carabobo"  ,  "Frequency" :  36  }, 
-  {  "Value" :  "CT"  ,  "Frequency" :  34  }, 
-  {  "Value" :  "MN"  ,  "Frequency" :  33  }, 
-  {  "Value" :  "Distrito Federal"  ,  "Frequency" :  32  }, 
-  {  "Value" :  "IA"  ,  "Frequency" :  31  }, 
-  {  "Value" :  "KS"  ,  "Frequency" :  29  }, 
-  {  "Value" :  "WI"  ,  "Frequency" :  28  }, 
-  {  "Value" :  "Zulia"  ,  "Frequency" :  26  }, 
-  {  "Value" :  "CO"  ,  "Frequency" :  24  }, 
-  {  "Value" :  "HI"  ,  "Frequency" :  23  }, 
-  {  "Value" :  "ON"  ,  "Frequency" :  23  }, 
-  {  "Value" :  "Peravia"  ,  "Frequency" :  22  }, 
-  {  "Value" :  "Santiago"  ,  "Frequency" :  22  }, 
-  {  "Value" :  "NV"  ,  "Frequency" :  21  }, 
-  {  "Value" :  "BC"  ,  "Frequency" :  20  }, 
-  {  "Value" :  "La Habana"  ,  "Frequency" :  20  }, 
-  {  "Value" :  "Anzoategui"  ,  "Frequency" :  19  }, 
-  {  "Value" :  "AR"  ,  "Frequency" :  19  }, 
-  {  "Value" :  "Aragua"  ,  "Frequency" :  19  }, 
-  {  "Value" :  "NE"  ,  "Frequency" :  17  }, 
-  {  "Value" :  "Bolivar"  ,  "Frequency" :  16  }
-]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 
-  {  "x" :  "CA"  ,  "Freq" :  826  }, 
-  {  "x" :  "TX"  ,  "Freq" :  293  }, 
-  {  "x" :  "FL"  ,  "Freq" :  260  }, 
-  {  "x" :  "NY"  ,  "Freq" :  155  }, 
-  {  "x" :  "IL"  ,  "Freq" :  154  }, 
-  {  "x" :  "OH"  ,  "Freq" :  150  }, 
-  {  "x" :  "PA"  ,  "Freq" :  124  }, 
-  {  "x" :  "GA"  ,  "Freq" :  115  }, 
-  {  "x" :  "Distrito Nacional"  ,  "Freq" :  92  }, 
-  {  "x" :  "other"  ,  "Freq" :  2284  }
+  {  "ww" :  "CA"  ,  "Freq" :  826  }, 
+  {  "ww" :  "TX"  ,  "Freq" :  293  }, 
+  {  "ww" :  "FL"  ,  "Freq" :  260  }, 
+  {  "ww" :  "NY"  ,  "Freq" :  155  }, 
+  {  "ww" :  "IL"  ,  "Freq" :  154  }, 
+  {  "ww" :  "OH"  ,  "Freq" :  150  }, 
+  {  "ww" :  "Distrito"  ,  "Freq" :  124  }, 
+  {  "ww" :  "PA"  ,  "Freq" :  124  }, 
+  {  "ww" :  "GA"  ,  "Freq" :  115  }, 
+  {  "ww" :  "San"  ,  "Freq" :  108  }, 
+  {  "ww" :  "Nacional"  ,  "Freq" :  92  }, 
+  {  "ww" :  "MI"  ,  "Freq" :  88  }, 
+  {  "ww" :  "VA"  ,  "Freq" :  76  }, 
+  {  "ww" :  "LA"  ,  "Freq" :  75  }, 
+  {  "ww" :  "NJ"  ,  "Freq" :  75  }, 
+  {  "ww" :  "NC"  ,  "Freq" :  71  }, 
+  {  "ww" :  "MO"  ,  "Freq" :  68  }, 
+  {  "ww" :  "de"  ,  "Freq" :  63  }, 
+  {  "ww" :  "TN"  ,  "Freq" :  62  }, 
+  {  "ww" :  "AL"  ,  "Freq" :  60  }, 
+  {  "ww" :  "WA"  ,  "Freq" :  59  }, 
+  {  "ww" :  "MA"  ,  "Freq" :  58  }, 
+  {  "ww" :  "Macoris"  ,  "Freq" :  58  }, 
+  {  "ww" :  "Pedro"  ,  "Freq" :  58  }, 
+  {  "ww" :  "KY"  ,  "Freq" :  57  }, 
+  {  "ww" :  "OK"  ,  "Freq" :  55  }, 
+  {  "ww" :  "MS"  ,  "Freq" :  54  }, 
+  {  "ww" :  "La"  ,  "Freq" :  49  }, 
+  {  "ww" :  "SC"  ,  "Freq" :  48  }, 
+  {  "ww" :  "MD"  ,  "Freq" :  42  }, 
+  {  "ww" :  "AZ"  ,  "Freq" :  41  }, 
+  {  "ww" :  "Cristobal"  ,  "Freq" :  40  }, 
+  {  "ww" :  "Carabobo"  ,  "Freq" :  36  }, 
+  {  "ww" :  "CT"  ,  "Freq" :  34  }, 
+  {  "ww" :  "MN"  ,  "Freq" :  33  }, 
+  {  "ww" :  "Federal"  ,  "Freq" :  32  }, 
+  {  "ww" :  "IA"  ,  "Freq" :  31  }, 
+  {  "ww" :  "KS"  ,  "Freq" :  29  }, 
+  {  "ww" :  "WI"  ,  "Freq" :  28  }, 
+  {  "ww" :  "Zulia"  ,  "Freq" :  26  }, 
+  {  "ww" :  "Santiago"  ,  "Freq" :  25  }, 
+  {  "ww" :  "CO"  ,  "Freq" :  24  }, 
+  {  "ww" :  "HI"  ,  "Freq" :  23  }, 
+  {  "ww" :  "Peravia"  ,  "Freq" :  22  }, 
+  {  "ww" :  "NV"  ,  "Freq" :  21  }, 
+  {  "ww" :  "BC"  ,  "Freq" :  20  }, 
+  {  "ww" :  "Habana"  ,  "Freq" :  20  }, 
+  {  "ww" :  "Anzoategui"  ,  "Freq" :  19  }, 
+  {  "ww" :  "AR"  ,  "Freq" :  19  }, 
+  {  "ww" :  "Aragua"  ,  "Freq" :  19  }
 ]</t>
   </si>
   <si>
@@ -1065,212 +1073,76 @@
     <t xml:space="preserve">  { 
     "breaks"  :  [ 
 165, 
-    166.5, 
-    168, 
-    169.5, 
-    171, 
-    172.5, 
-    174, 
-    175.5, 
-    177, 
-    178.5, 
+    170, 
+    175, 
     180, 
-    181.5, 
-    183, 
-    184.5, 
-    186, 
-    187.5, 
-    189, 
-    190.5, 
-    192, 
-    193.5, 
+    185, 
+    190, 
     195, 
-    196.5, 
-    198, 
-    199.5, 
-    201, 
-    202.5, 
-    204, 
-    205.5, 
-    207, 
-    208.5, 
+    200, 
+    205, 
     210, 
-    211.5, 
-    213, 
-    214.5, 
-    216, 
-    217.5, 
-    219, 
-    220.5, 
-    222, 
-    223.5, 
+    215, 
+    220, 
     225, 
-    226.5, 
-    228, 
-    229.5, 
-    231, 
-    232.5, 
-    234, 
-    235.5, 
-    237, 
-    238.5, 
-    240
+    230, 
+    235, 
+    240, 
+    245
 ], 
     "density"  :  [ 
-0.0235, 
-    0.0012, 
-    0.0002, 
-    0.0425, 
-    0.0035, 
-    0.0028, 
-    0.0563, 
-    0.0014, 
-    0.003, 
-    0.0762, 
-    0.0007, 
-    0.003, 
-    0.0012, 
-    0.0914, 
-    0.003, 
-    0.003, 
-    0.0918, 
-    0.0049, 
-    0.0026, 
-    0.0869, 
-    0.0012, 
-    0.0049, 
-    0.0007, 
-    0.0944, 
-    0.0023, 
-    0.0019, 
-    0.0728, 
-    0.003, 
-    0.0012, 
-    0.0718, 
-    0.0016, 
-    0.0051, 
-    0.0007, 
-    0.0607, 
-    0.0026, 
-    0.0035, 
-    0.0511, 
-    0.0019, 
-    0.0016, 
-    0.0386, 
-    0.0005, 
-    0.0026, 
-    0.0009, 
-    0.0281, 
-    0.0016, 
-    0.0016, 
-    0.023, 
-    0.0007, 
-    0.0007, 
-    0.0198
+0.0249, 
+    0.0488, 
+    0.0609, 
+    0.0809, 
+    0.0974, 
+    0.1013, 
+    0.0916, 
+    0.0986, 
+    0.0788, 
+    0.0774, 
+    0.0667, 
+    0.0556, 
+    0.0416, 
+    0.0314, 
+    0.0249, 
+    0.0193
 ], 
     "y"  :  [ 
-101, 
-    5, 
-    1, 
-    183, 
-    15, 
-    12, 
-    242, 
-    6, 
-    13, 
-    328, 
-    3, 
-    13, 
-    5, 
-    393, 
-    13, 
-    13, 
-    395, 
-    21, 
-    11, 
-    374, 
-    5, 
-    21, 
-    3, 
-    406, 
-    10, 
-    8, 
-    313, 
-    13, 
-    5, 
-    309, 
-    7, 
-    22, 
-    3, 
-    261, 
-    11, 
-    15, 
-    220, 
-    8, 
-    7, 
-    166, 
-    2, 
-    11, 
-    4, 
-    121, 
-    7, 
-    7, 
-    99, 
-    3, 
-    3, 
-    85
+107, 
+    210, 
+    262, 
+    348, 
+    419, 
+    436, 
+    394, 
+    424, 
+    339, 
+    333, 
+    287, 
+    239, 
+    179, 
+    135, 
+    107, 
+    83
 ], 
     "mids"  :  [ 
-165.75, 
-    167.25, 
-    168.75, 
-    170.25, 
-    171.75, 
-    173.25, 
-    174.75, 
-    176.25, 
-    177.75, 
-    179.25, 
-    180.75, 
-    182.25, 
-    183.75, 
-    185.25, 
-    186.75, 
-    188.25, 
-    189.75, 
-    191.25, 
-    192.75, 
-    194.25, 
-    195.75, 
-    197.25, 
-    198.75, 
-    200.25, 
-    201.75, 
-    203.25, 
-    204.75, 
-    206.25, 
-    207.75, 
-    209.25, 
-    210.75, 
-    212.25, 
-    213.75, 
-    215.25, 
-    216.75, 
-    218.25, 
-    219.75, 
-    221.25, 
-    222.75, 
-    224.25, 
-    225.75, 
-    227.25, 
-    228.75, 
-    230.25, 
-    231.75, 
-    233.25, 
-    234.75, 
-    236.25, 
-    237.75, 
-    239.25
+167.5, 
+    172.5, 
+    177.5, 
+    182.5, 
+    187.5, 
+    192.5, 
+    197.5, 
+    202.5, 
+    207.5, 
+    212.5, 
+    217.5, 
+    222.5, 
+    227.5, 
+    232.5, 
+    237.5, 
+    242.5
 ], 
     "mean"  :  [ 
 199.579
@@ -1350,212 +1222,44 @@
     <t xml:space="preserve">  { 
     "breaks"  :  [ 
 70, 
-    70.14, 
-    70.28, 
-    70.42, 
-    70.56, 
-    70.7, 
-    70.84, 
-    70.98, 
-    71.12, 
-    71.26, 
-    71.4, 
-    71.54, 
-    71.68, 
-    71.82, 
-    71.96, 
-    72.1, 
-    72.24, 
-    72.38, 
-    72.52, 
-    72.66, 
-    72.8, 
-    72.94, 
-    73.08, 
-    73.22, 
-    73.36, 
-    73.5, 
-    73.64, 
-    73.78, 
-    73.92, 
-    74.06, 
-    74.2, 
-    74.34, 
-    74.48, 
-    74.62, 
-    74.76, 
-    74.9, 
-    75.04, 
-    75.18, 
-    75.32, 
-    75.46, 
-    75.6, 
-    75.74, 
-    75.88, 
-    76.02, 
-    76.16, 
-    76.3, 
-    76.44, 
-    76.58, 
-    76.72, 
-    76.86, 
-    77
+    71, 
+    72, 
+    73, 
+    74, 
+    75, 
+    76, 
+    77, 
+    78
 ], 
     "density"  :  [ 
 0.0618, 
-    0, 
-    0, 
-    0, 
-    0, 
-    0, 
-    0, 
     0.0972, 
-    0, 
-    0, 
-    0, 
-    0, 
-    0, 
-    0, 
     0.163, 
-    0, 
-    0, 
-    0, 
-    0, 
-    0, 
-    0, 
     0.1674, 
-    0, 
-    0, 
-    0, 
-    0, 
-    0, 
-    0, 
     0.1955, 
-    0, 
-    0, 
-    0, 
-    0, 
-    0, 
-    0, 
     0.1566, 
-    0, 
-    0, 
-    0, 
-    0, 
-    0, 
-    0, 
     0.104, 
-    0, 
-    0, 
-    0, 
-    0, 
-    0, 
-    0, 
     0.0546
 ], 
     "y"  :  [ 
 264, 
-    0, 
-    0, 
-    0, 
-    0, 
-    0, 
-    0, 
     415, 
-    0, 
-    0, 
-    0, 
-    0, 
-    0, 
-    0, 
     696, 
-    0, 
-    0, 
-    0, 
-    0, 
-    0, 
-    0, 
     715, 
-    0, 
-    0, 
-    0, 
-    0, 
-    0, 
-    0, 
     835, 
-    0, 
-    0, 
-    0, 
-    0, 
-    0, 
-    0, 
     669, 
-    0, 
-    0, 
-    0, 
-    0, 
-    0, 
-    0, 
     444, 
-    0, 
-    0, 
-    0, 
-    0, 
-    0, 
-    0, 
     233
 ], 
     "mids"  :  [ 
-70.07, 
-    70.21, 
-    70.35, 
-    70.49, 
-    70.63, 
-    70.77, 
-    70.91, 
-    71.05, 
-    71.19, 
-    71.33, 
-    71.47, 
-    71.61, 
-    71.75, 
-    71.89, 
-    72.03, 
-    72.17, 
-    72.31, 
-    72.45, 
-    72.59, 
-    72.73, 
-    72.87, 
-    73.01, 
-    73.15, 
-    73.29, 
-    73.43, 
-    73.57, 
-    73.71, 
-    73.85, 
-    73.99, 
-    74.13, 
-    74.27, 
-    74.41, 
-    74.55, 
-    74.69, 
-    74.83, 
-    74.97, 
-    75.11, 
-    75.25, 
-    75.39, 
-    75.53, 
-    75.67, 
-    75.81, 
-    75.95, 
-    76.09, 
-    76.23, 
-    76.37, 
-    76.51, 
-    76.65, 
-    76.79, 
-    76.93
+70.5, 
+    71.5, 
+    72.5, 
+    73.5, 
+    74.5, 
+    75.5, 
+    76.5, 
+    77.5
 ], 
     "mean"  :  [ 
 73.4877
@@ -1748,9 +1452,6 @@
 27</t>
   </si>
   <si>
-    <t xml:space="preserve">42 ;; 50 ;; 47 ;; 54 ;; 27</t>
-  </si>
-  <si>
     <t xml:space="preserve">[ 
   {  "STAT" :  "Rows"  ,  "VAL" :  "4,620"  ,  "PER" :  ""  }, 
   {  "STAT" :  "Distinct"  ,  "VAL" :  "149"  ,  "PER" :  "(3.2%)"  }
@@ -1776,213 +1477,169 @@
   <si>
     <t xml:space="preserve">  { 
     "breaks"  :  [ 
-17, 
-    19.26, 
-    21.52, 
-    23.78, 
-    26.04, 
-    28.3, 
-    30.56, 
-    32.82, 
-    35.08, 
-    37.34, 
-    39.6, 
-    41.86, 
-    44.12, 
-    46.38, 
-    48.64, 
-    50.9, 
-    53.16, 
-    55.42, 
-    57.68, 
-    59.94, 
-    62.2, 
-    64.46, 
-    66.72, 
-    68.98, 
-    71.24, 
-    73.5, 
-    75.76, 
-    78.02, 
-    80.28, 
-    82.54, 
-    84.8, 
-    87.06, 
-    89.32, 
-    91.58, 
-    93.84, 
-    96.1, 
-    98.36, 
-    100.62, 
-    102.88, 
-    105.14, 
-    107.4, 
-    109.66, 
-    111.92, 
-    114.18, 
-    116.44, 
-    118.7, 
-    120.96, 
-    123.22, 
-    125.48, 
-    127.74, 
-    130
+15, 
+    18, 
+    21, 
+    24, 
+    27, 
+    30, 
+    33, 
+    36, 
+    39, 
+    42, 
+    45, 
+    48, 
+    51, 
+    54, 
+    57, 
+    60, 
+    63, 
+    66, 
+    69, 
+    72, 
+    75, 
+    78, 
+    81, 
+    84, 
+    87, 
+    90, 
+    93, 
+    96, 
+    99, 
+    102, 
+    105, 
+    108, 
+    111, 
+    114, 
+    117, 
+    120, 
+    123, 
+    126, 
+    129, 
+    132
 ], 
     "density"  :  [ 
-0.0296, 
-    0.0203, 
-    0.0251, 
+0.0079, 
+    0.0335, 
+    0.0337, 
     0.059, 
-    0.0428, 
-    0.0509, 
-    0.0447, 
+    0.0657, 
+    0.0727, 
     0.0452, 
+    0.0394, 
+    0.0387, 
+    0.0359, 
+    0.0325, 
+    0.0402, 
+    0.0323, 
+    0.0368, 
     0.0261, 
-    0.0258, 
-    0.0263, 
-    0.0359, 
-    0.0234, 
-    0.0246, 
-    0.0246, 
-    0.0323, 
-    0.0246, 
-    0.021, 
-    0.0172, 
     0.0277, 
+    0.0217, 
+    0.0177, 
+    0.017, 
+    0.0191, 
+    0.01, 
+    0.0186, 
+    0.0139, 
+    0.0194, 
     0.0151, 
+    0.016, 
+    0.0139, 
+    0.0194, 
+    0.0194, 
+    0.0167, 
+    0.0151, 
+    0.0201, 
+    0.0174, 
+    0.0158, 
+    0.0158, 
+    0.016, 
     0.0129, 
-    0.0115, 
-    0.017, 
-    0.0127, 
-    0.0105, 
-    0.0117, 
-    0.0129, 
-    0.0105, 
-    0.01, 
-    0.0165, 
-    0.0112, 
-    0.0096, 
-    0.0117, 
-    0.0151, 
-    0.0129, 
-    0.0141, 
-    0.0108, 
-    0.0155, 
-    0.0108, 
-    0.0134, 
-    0.0115, 
-    0.0189, 
-    0.0096, 
-    0.0091, 
-    0.0127, 
-    0.0151, 
-    0.0079, 
-    0.0074, 
-    0.0146
+    0.0124, 
+    0.0096
 ], 
     "y"  :  [ 
-124, 
-    85, 
-    105, 
+33, 
+    140, 
+    141, 
     247, 
-    179, 
-    213, 
-    187, 
+    275, 
+    304, 
     189, 
+    165, 
+    162, 
+    150, 
+    136, 
+    168, 
+    135, 
+    154, 
     109, 
-    108, 
-    110, 
-    150, 
-    98, 
-    103, 
-    103, 
-    135, 
-    103, 
-    88, 
-    72, 
     116, 
+    91, 
+    74, 
+    71, 
+    80, 
+    42, 
+    78, 
+    58, 
+    81, 
     63, 
+    67, 
+    58, 
+    81, 
+    81, 
+    70, 
+    63, 
+    84, 
+    73, 
+    66, 
+    66, 
+    67, 
     54, 
-    48, 
-    71, 
-    53, 
-    44, 
-    49, 
-    54, 
-    44, 
-    42, 
-    69, 
-    47, 
-    40, 
-    49, 
-    63, 
-    54, 
-    59, 
-    45, 
-    65, 
-    45, 
-    56, 
-    48, 
-    79, 
-    40, 
-    38, 
-    53, 
-    63, 
-    33, 
-    31, 
-    61
+    52, 
+    40
 ], 
     "mids"  :  [ 
-18.13, 
-    20.39, 
-    22.65, 
-    24.91, 
-    27.17, 
-    29.43, 
-    31.69, 
-    33.95, 
-    36.21, 
-    38.47, 
-    40.73, 
-    42.99, 
-    45.25, 
-    47.51, 
-    49.77, 
-    52.03, 
-    54.29, 
-    56.55, 
-    58.81, 
-    61.07, 
-    63.33, 
-    65.59, 
-    67.85, 
-    70.11, 
-    72.37, 
-    74.63, 
-    76.89, 
-    79.15, 
-    81.41, 
-    83.67, 
-    85.93, 
-    88.19, 
-    90.45, 
-    92.71, 
-    94.97, 
-    97.23, 
-    99.49, 
-    101.75, 
-    104.01, 
-    106.27, 
-    108.53, 
-    110.79, 
-    113.05, 
-    115.31, 
-    117.57, 
-    119.83, 
-    122.09, 
-    124.35, 
-    126.61, 
-    128.87
+16.5, 
+    19.5, 
+    22.5, 
+    25.5, 
+    28.5, 
+    31.5, 
+    34.5, 
+    37.5, 
+    40.5, 
+    43.5, 
+    46.5, 
+    49.5, 
+    52.5, 
+    55.5, 
+    58.5, 
+    61.5, 
+    64.5, 
+    67.5, 
+    70.5, 
+    73.5, 
+    76.5, 
+    79.5, 
+    82.5, 
+    85.5, 
+    88.5, 
+    91.5, 
+    94.5, 
+    97.5, 
+    100.5, 
+    103.5, 
+    106.5, 
+    109.5, 
+    112.5, 
+    115.5, 
+    118.5, 
+    121.5, 
+    124.5, 
+    127.5, 
+    130.5
 ], 
     "mean"  :  [ 
 60.7325
@@ -2018,6 +1675,9 @@
 21</t>
   </si>
   <si>
+    <t xml:space="preserve">identifier</t>
+  </si>
+  <si>
     <t xml:space="preserve">[ 
   {  "STAT" :  "Rows"  ,  "VAL" :  "4,620"  ,  "PER" :  ""  }, 
   {  "STAT" :  "Distinct"  ,  "VAL" :  "581"  ,  "PER" :  "(12.6%)"  }, 
@@ -2044,213 +1704,205 @@
   <si>
     <t xml:space="preserve">  { 
     "breaks"  :  [ 
-1, 
-    10.46, 
-    19.92, 
-    29.38, 
-    38.84, 
-    48.3, 
-    57.76, 
-    67.22, 
-    76.68, 
-    86.14, 
-    95.6, 
-    105.06, 
-    114.52, 
-    123.98, 
-    133.44, 
-    142.9, 
-    152.36, 
-    161.82, 
-    171.28, 
-    180.74, 
-    190.2, 
-    199.66, 
-    209.12, 
-    218.58, 
-    228.04, 
-    237.5, 
-    246.96, 
-    256.42, 
-    265.88, 
-    275.34, 
-    284.8, 
-    294.26, 
-    303.72, 
-    313.18, 
-    322.64, 
-    332.1, 
-    341.56, 
-    351.02, 
-    360.48, 
-    369.94, 
-    379.4, 
-    388.86, 
-    398.32, 
-    407.78, 
-    417.24, 
-    426.7, 
-    436.16, 
-    445.62, 
-    455.08, 
-    464.54, 
-    474
+0, 
+    10, 
+    20, 
+    30, 
+    40, 
+    50, 
+    60, 
+    70, 
+    80, 
+    90, 
+    100, 
+    110, 
+    120, 
+    130, 
+    140, 
+    150, 
+    160, 
+    170, 
+    180, 
+    190, 
+    200, 
+    210, 
+    220, 
+    230, 
+    240, 
+    250, 
+    260, 
+    270, 
+    280, 
+    290, 
+    300, 
+    310, 
+    320, 
+    330, 
+    340, 
+    350, 
+    360, 
+    370, 
+    380, 
+    390, 
+    400, 
+    410, 
+    420, 
+    430, 
+    440, 
+    450, 
+    460, 
+    470, 
+    480
 ], 
     "density"  :  [ 
-0.2534, 
-    0.0465, 
+0.2462, 
+    0.0536, 
     0.0462, 
-    0.0438, 
-    0.0478, 
-    0.029, 
-    0.0195, 
-    0.0135, 
+    0.048, 
+    0.0462, 
+    0.0309, 
+    0.0187, 
+    0.0137, 
+    0.0174, 
+    0.0166, 
+    0.0161, 
+    0.0145, 
     0.0179, 
+    0.0143, 
     0.0121, 
     0.0172, 
+    0.0179, 
+    0.0148, 
+    0.0137, 
+    0.0121, 
+    0.0119, 
+    0.0095, 
     0.014, 
-    0.0143, 
-    0.0161, 
     0.0145, 
+    0.0135, 
+    0.014, 
+    0.0135, 
+    0.0132, 
+    0.0111, 
+    0.0137, 
+    0.009, 
     0.0113, 
-    0.0185, 
-    0.0145, 
-    0.0145, 
-    0.0132, 
+    0.0077, 
     0.0106, 
+    0.0135, 
+    0.0106, 
+    0.0124, 
+    0.0098, 
+    0.0084, 
+    0.014, 
+    0.01, 
+    0.0098, 
+    0.0124, 
+    0.0082, 
     0.0119, 
+    0.0106, 
     0.0092, 
-    0.0127, 
-    0.0137, 
-    0.0119, 
-    0.0153, 
-    0.0087, 
-    0.0161, 
-    0.0098, 
-    0.0135, 
-    0.0092, 
-    0.0106, 
-    0.0098, 
-    0.0082, 
-    0.009, 
-    0.0129, 
-    0.0095, 
-    0.0119, 
-    0.0098, 
-    0.0077, 
-    0.0135, 
-    0.0095, 
-    0.01, 
-    0.0108, 
-    0.0077, 
-    0.0111, 
-    0.0111, 
-    0.0095, 
-    0.0074
+    0.0037
 ], 
     "y"  :  [ 
-960, 
-    176, 
+933, 
+    203, 
     175, 
-    166, 
-    181, 
-    110, 
-    74, 
-    51, 
+    182, 
+    175, 
+    117, 
+    71, 
+    52, 
+    66, 
+    63, 
+    61, 
+    55, 
     68, 
+    54, 
     46, 
     65, 
+    68, 
+    56, 
+    52, 
+    46, 
+    45, 
+    36, 
     53, 
-    54, 
-    61, 
     55, 
+    51, 
+    53, 
+    51, 
+    50, 
+    42, 
+    52, 
+    34, 
     43, 
-    70, 
-    55, 
-    55, 
-    50, 
+    29, 
     40, 
+    51, 
+    40, 
+    47, 
+    37, 
+    32, 
+    53, 
+    38, 
+    37, 
+    47, 
+    31, 
     45, 
+    40, 
     35, 
-    48, 
-    52, 
-    45, 
-    58, 
-    33, 
-    61, 
-    37, 
-    51, 
-    35, 
-    40, 
-    37, 
-    31, 
-    34, 
-    49, 
-    36, 
-    45, 
-    37, 
-    29, 
-    51, 
-    36, 
-    38, 
-    41, 
-    29, 
-    42, 
-    42, 
-    36, 
-    28
+    14
 ], 
     "mids"  :  [ 
-5.73, 
-    15.19, 
-    24.65, 
-    34.11, 
-    43.57, 
-    53.03, 
-    62.49, 
-    71.95, 
-    81.41, 
-    90.87, 
-    100.33, 
-    109.79, 
-    119.25, 
-    128.71, 
-    138.17, 
-    147.63, 
-    157.09, 
-    166.55, 
-    176.01, 
-    185.47, 
-    194.93, 
-    204.39, 
-    213.85, 
-    223.31, 
-    232.77, 
-    242.23, 
-    251.69, 
-    261.15, 
-    270.61, 
-    280.07, 
-    289.53, 
-    298.99, 
-    308.45, 
-    317.91, 
-    327.37, 
-    336.83, 
-    346.29, 
-    355.75, 
-    365.21, 
-    374.67, 
-    384.13, 
-    393.59, 
-    403.05, 
-    412.51, 
-    421.97, 
-    431.43, 
-    440.89, 
-    450.35, 
-    459.81, 
-    469.27
+5, 
+    15, 
+    25, 
+    35, 
+    45, 
+    55, 
+    65, 
+    75, 
+    85, 
+    95, 
+    105, 
+    115, 
+    125, 
+    135, 
+    145, 
+    155, 
+    165, 
+    175, 
+    185, 
+    195, 
+    205, 
+    215, 
+    225, 
+    235, 
+    245, 
+    255, 
+    265, 
+    275, 
+    285, 
+    295, 
+    305, 
+    315, 
+    325, 
+    335, 
+    345, 
+    355, 
+    365, 
+    375, 
+    385, 
+    395, 
+    405, 
+    415, 
+    425, 
+    435, 
+    445, 
+    455, 
+    465, 
+    475
 ], 
     "mean"  :  [ 
 157.7442
@@ -2313,212 +1965,184 @@
     <t xml:space="preserve">  { 
     "breaks"  :  [ 
 0, 
-    2.56, 
-    5.12, 
-    7.68, 
-    10.24, 
-    12.8, 
-    15.36, 
-    17.92, 
-    20.48, 
-    23.04, 
-    25.6, 
-    28.16, 
-    30.72, 
-    33.28, 
-    35.84, 
-    38.4, 
-    40.96, 
-    43.52, 
-    46.08, 
-    48.64, 
-    51.2, 
-    53.76, 
-    56.32, 
-    58.88, 
-    61.44, 
-    64, 
-    66.56, 
-    69.12, 
-    71.68, 
-    74.24, 
-    76.8, 
-    79.36, 
-    81.92, 
-    84.48, 
-    87.04, 
-    89.6, 
-    92.16, 
-    94.72, 
-    97.28, 
-    99.84, 
-    102.4, 
-    104.96, 
-    107.52, 
-    110.08, 
-    112.64, 
-    115.2, 
-    117.76, 
-    120.32, 
-    122.88, 
-    125.44, 
-    128
+    3, 
+    6, 
+    9, 
+    12, 
+    15, 
+    18, 
+    21, 
+    24, 
+    27, 
+    30, 
+    33, 
+    36, 
+    39, 
+    42, 
+    45, 
+    48, 
+    51, 
+    54, 
+    57, 
+    60, 
+    63, 
+    66, 
+    69, 
+    72, 
+    75, 
+    78, 
+    81, 
+    84, 
+    87, 
+    90, 
+    93, 
+    96, 
+    99, 
+    102, 
+    105, 
+    108, 
+    111, 
+    114, 
+    117, 
+    120, 
+    123, 
+    126, 
+    129
 ], 
     "density"  :  [ 
 0.4233, 
     0.069, 
-    0.028, 
-    0.0257, 
-    0.0105, 
-    0.013, 
-    0.0114, 
+    0.0412, 
+    0.0168, 
+    0.0168, 
+    0.0137, 
     0.0171, 
     0.0164, 
+    0.0155, 
+    0.0159, 
+    0.0157, 
+    0.0146, 
+    0.0166, 
+    0.0146, 
+    0.0141, 
+    0.0118, 
+    0.0116, 
+    0.0102, 
+    0.0141, 
+    0.0105, 
+    0.0153, 
+    0.0105, 
+    0.0112, 
+    0.0132, 
     0.01, 
-    0.0155, 
-    0.0107, 
-    0.0159, 
+    0.01, 
+    0.0091, 
+    0.0116, 
+    0.0087, 
+    0.0102, 
+    0.0091, 
     0.0096, 
-    0.0166, 
-    0.0091, 
-    0.0146, 
-    0.0123, 
-    0.0087, 
-    0.01, 
-    0.0077, 
-    0.0141, 
-    0.0068, 
-    0.0143, 
-    0.0112, 
-    0.0071, 
-    0.0125, 
-    0.0087, 
-    0.01, 
-    0.0071, 
-    0.0087, 
-    0.0075, 
-    0.0102, 
-    0.0089, 
-    0.0073, 
-    0.0091, 
-    0.0064, 
-    0.0087, 
+    0.0096, 
+    0.0114, 
     0.0082, 
-    0.0102, 
-    0.0052, 
     0.0087, 
     0.0096, 
-    0.0059, 
-    0.0102, 
-    0.0052, 
-    0.0052, 
-    0.0039, 
+    0.0082, 
+    0.0116, 
+    0.005, 
+    0.0057, 
     0.0084, 
     0.0057
 ], 
     "y"  :  [ 
 1859, 
     303, 
-    123, 
-    113, 
-    46, 
-    57, 
-    50, 
+    181, 
+    74, 
+    74, 
+    60, 
     75, 
     72, 
+    68, 
+    70, 
+    69, 
+    64, 
+    73, 
+    64, 
+    62, 
+    52, 
+    51, 
+    45, 
+    62, 
+    46, 
+    67, 
+    46, 
+    49, 
+    58, 
     44, 
-    68, 
-    47, 
-    70, 
+    44, 
+    40, 
+    51, 
+    38, 
+    45, 
+    40, 
     42, 
-    73, 
-    40, 
-    64, 
-    54, 
-    38, 
-    44, 
-    34, 
-    62, 
-    30, 
-    63, 
-    49, 
-    31, 
-    55, 
-    38, 
-    44, 
-    31, 
-    38, 
-    33, 
-    45, 
-    39, 
-    32, 
-    40, 
-    28, 
-    38, 
+    42, 
+    50, 
     36, 
-    45, 
-    23, 
     38, 
     42, 
-    26, 
-    45, 
-    23, 
-    23, 
-    17, 
+    36, 
+    51, 
+    22, 
+    25, 
     37, 
     25
 ], 
     "mids"  :  [ 
-1.28, 
-    3.84, 
-    6.4, 
-    8.96, 
-    11.52, 
-    14.08, 
-    16.64, 
-    19.2, 
-    21.76, 
-    24.32, 
-    26.88, 
-    29.44, 
-    32, 
-    34.56, 
-    37.12, 
-    39.68, 
-    42.24, 
-    44.8, 
-    47.36, 
-    49.92, 
-    52.48, 
-    55.04, 
-    57.6, 
-    60.16, 
-    62.72, 
-    65.28, 
-    67.84, 
-    70.4, 
-    72.96, 
-    75.52, 
-    78.08, 
-    80.64, 
-    83.2, 
-    85.76, 
-    88.32, 
-    90.88, 
-    93.44, 
-    96, 
-    98.56, 
-    101.12, 
-    103.68, 
-    106.24, 
-    108.8, 
-    111.36, 
-    113.92, 
-    116.48, 
-    119.04, 
-    121.6, 
-    124.16, 
-    126.72
+1.5, 
+    4.5, 
+    7.5, 
+    10.5, 
+    13.5, 
+    16.5, 
+    19.5, 
+    22.5, 
+    25.5, 
+    28.5, 
+    31.5, 
+    34.5, 
+    37.5, 
+    40.5, 
+    43.5, 
+    46.5, 
+    49.5, 
+    52.5, 
+    55.5, 
+    58.5, 
+    61.5, 
+    64.5, 
+    67.5, 
+    70.5, 
+    73.5, 
+    76.5, 
+    79.5, 
+    82.5, 
+    85.5, 
+    88.5, 
+    91.5, 
+    94.5, 
+    97.5, 
+    100.5, 
+    103.5, 
+    106.5, 
+    109.5, 
+    112.5, 
+    115.5, 
+    118.5, 
+    121.5, 
+    124.5, 
+    127.5
 ], 
     "mean"  :  [ 
 34.4208
@@ -3141,213 +2765,217 @@
   <si>
     <t xml:space="preserve">  { 
     "breaks"  :  [ 
-109000, 
-    210010.72, 
-    311021.44, 
-    412032.16, 
-    513042.88, 
-    614053.6, 
-    715064.32, 
-    816075.04, 
-    917085.76, 
-    1018096.48, 
-    1119107.2, 
-    1220117.92, 
-    1321128.64, 
-    1422139.36, 
-    1523150.08, 
-    1624160.8, 
-    1725171.52, 
-    1826182.24, 
-    1927192.96, 
-    2028203.68, 
-    2129214.4, 
-    2230225.12, 
-    2331235.84, 
-    2432246.56, 
-    2533257.28, 
-    2634268, 
-    2735278.72, 
-    2836289.44, 
-    2937300.16, 
-    3038310.88, 
-    3139321.6, 
-    3240332.32, 
-    3341343.04, 
-    3442353.76, 
-    3543364.48, 
-    3644375.2, 
-    3745385.92, 
-    3846396.64, 
-    3947407.36, 
-    4048418.08, 
-    4149428.8, 
-    4250439.52, 
-    4351450.24, 
-    4452460.96, 
-    4553471.68, 
-    4654482.4, 
-    4755493.12, 
-    4856503.84, 
-    4957514.56, 
-    5058525.28, 
-    5159536
+101011, 
+    202022, 
+    303033, 
+    404044, 
+    505055, 
+    606066, 
+    707077, 
+    808088, 
+    909099, 
+    1010110, 
+    1111121, 
+    1212132, 
+    1313143, 
+    1414154, 
+    1515165, 
+    1616176, 
+    1717187, 
+    1818198, 
+    1919209, 
+    2020220, 
+    2121231, 
+    2222242, 
+    2323253, 
+    2424264, 
+    2525275, 
+    2626286, 
+    2727297, 
+    2828308, 
+    2929319, 
+    3030330, 
+    3131341, 
+    3232352, 
+    3333363, 
+    3434374, 
+    3535385, 
+    3636396, 
+    3737407, 
+    3838418, 
+    3939429, 
+    4040440, 
+    4141451, 
+    4242462, 
+    4343473, 
+    4444484, 
+    4545495, 
+    4646506, 
+    4747517, 
+    4848528, 
+    4949539, 
+    5050550, 
+    5151561, 
+    5252572
 ], 
     "density"  :  [ 
-0.1601, 
-    0.0845, 
-    0.1153, 
-    0.1502, 
-    0.0809, 
-    0.0387, 
-    0.032, 
-    0.0292, 
-    0.024, 
-    0.0206, 
-    0.019, 
-    0.0168, 
+0.1471, 
+    0.0897, 
+    0.1127, 
+    0.1098, 
+    0.1305, 
+    0.0377, 
+    0.0318, 
+    0.0306, 
+    0.0237, 
+    0.0204, 
+    0.0192, 
     0.0159, 
+    0.0166, 
+    0.0142, 
+    0.0133, 
     0.0135, 
     0.0138, 
-    0.013, 
-    0.0138, 
-    0.0119, 
-    0.0109, 
+    0.0114, 
+    0.0112, 
     0.0074, 
     0.0095, 
-    0.0076, 
-    0.0097, 
+    0.0078, 
+    0.0104, 
+    0.0055, 
     0.0062, 
-    0.0059, 
-    0.0078, 
+    0.0081, 
     0.0055, 
     0.0047, 
+    0.0047, 
     0.0045, 
-    0.0052, 
+    0.0038, 
     0.0031, 
+    0.0057, 
+    0.0057, 
+    0.0043, 
+    0.0045, 
+    0.0036, 
+    0.004, 
     0.0038, 
-    0.0052, 
-    0.0055, 
-    0.0043, 
-    0.0047, 
-    0.0036, 
-    0.0038, 
-    0.0038, 
+    0.0021, 
     0.0024, 
-    0.0021, 
     0.0017, 
-    0.0021, 
+    0.0019, 
     0.0033, 
-    0.0007, 
+    0.0009, 
     0.0017, 
     0.004, 
     0.0028, 
-    0.0012, 
-    0.0021
+    0.0009, 
+    0.0017, 
+    0.0007
 ], 
     "y"  :  [ 
-675, 
-    356, 
-    486, 
-    633, 
-    341, 
-    163, 
-    135, 
-    123, 
-    101, 
-    87, 
-    80, 
-    71, 
+620, 
+    378, 
+    475, 
+    463, 
+    550, 
+    159, 
+    134, 
+    129, 
+    100, 
+    86, 
+    81, 
     67, 
+    70, 
+    60, 
+    56, 
     57, 
     58, 
-    55, 
-    58, 
-    50, 
-    46, 
+    48, 
+    47, 
     31, 
     40, 
-    32, 
-    41, 
+    33, 
+    44, 
+    23, 
     26, 
-    25, 
-    33, 
+    34, 
     23, 
     20, 
+    20, 
     19, 
-    22, 
+    16, 
     13, 
+    24, 
+    24, 
+    18, 
+    19, 
+    15, 
+    17, 
     16, 
-    22, 
-    23, 
-    18, 
-    20, 
-    15, 
-    16, 
-    16, 
+    9, 
     10, 
-    9, 
     7, 
-    9, 
+    8, 
     14, 
-    3, 
+    4, 
     7, 
     17, 
     12, 
-    5, 
-    9
+    4, 
+    7, 
+    3
 ], 
     "mids"  :  [ 
-159505.36, 
-    260516.08, 
-    361526.8, 
-    462537.52, 
-    563548.24, 
-    664558.96, 
-    765569.68, 
-    866580.4, 
-    967591.12, 
-    1068601.84, 
-    1169612.56, 
-    1270623.28, 
-    1371634, 
-    1472644.72, 
-    1573655.44, 
-    1674666.16, 
-    1775676.88, 
-    1876687.6, 
-    1977698.32, 
-    2078709.04, 
-    2179719.76, 
-    2280730.48, 
-    2381741.2, 
-    2482751.92, 
-    2583762.64, 
-    2684773.36, 
-    2785784.08, 
-    2886794.8, 
-    2987805.52, 
-    3088816.24, 
-    3189826.96, 
-    3290837.68, 
-    3391848.4, 
-    3492859.12, 
-    3593869.84, 
-    3694880.56, 
-    3795891.28, 
-    3896902, 
-    3997912.72, 
-    4098923.44, 
-    4199934.16, 
-    4300944.88, 
-    4401955.6, 
-    4502966.32, 
-    4603977.04, 
-    4704987.76, 
-    4805998.48, 
-    4907009.2, 
-    5008019.92, 
-    5109030.64
+151516.5, 
+    252527.5, 
+    353538.5, 
+    454549.5, 
+    555560.5, 
+    656571.5, 
+    757582.5, 
+    858593.5, 
+    959604.5, 
+    1060615.5, 
+    1161626.5, 
+    1262637.5, 
+    1363648.5, 
+    1464659.5, 
+    1565670.5, 
+    1666681.5, 
+    1767692.5, 
+    1868703.5, 
+    1969714.5, 
+    2070725.5, 
+    2171736.5, 
+    2272747.5, 
+    2373758.5, 
+    2474769.5, 
+    2575780.5, 
+    2676791.5, 
+    2777802.5, 
+    2878813.5, 
+    2979824.5, 
+    3080835.5, 
+    3181846.5, 
+    3282857.5, 
+    3383868.5, 
+    3484879.5, 
+    3585890.5, 
+    3686901.5, 
+    3787912.5, 
+    3888923.5, 
+    3989934.5, 
+    4090945.5, 
+    4191956.5, 
+    4292967.5, 
+    4393978.5, 
+    4494989.5, 
+    4596000.5, 
+    4697011.5, 
+    4798022.5, 
+    4899033.5, 
+    5000044.5, 
+    5101055.5, 
+    5202066.5
 ], 
     "mean"  :  [ 
 1269244.0615
@@ -13343,7 +12971,7 @@
         <v>3</v>
       </c>
       <c r="S2" s="6" t="n">
-        <v>0.865</v>
+        <v>0.5986</v>
       </c>
       <c r="T2" s="7" t="s">
         <v>44</v>
@@ -13361,7 +12989,7 @@
         <v>51</v>
       </c>
       <c r="Y2" s="7" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="Z2" s="7" t="s">
         <v>50</v>
@@ -13373,34 +13001,34 @@
         <v>44</v>
       </c>
       <c r="AC2" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD2" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE2" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="AD2" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE2" s="7" t="s">
+      <c r="AF2" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG2" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH2" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI2" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="AF2" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AG2" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH2" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI2" s="7" t="s">
+      <c r="AJ2" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="AJ2" s="7" t="s">
+      <c r="AK2" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="AK2" s="7" t="s">
+      <c r="AL2" s="7" t="s">
         <v>57</v>
-      </c>
-      <c r="AL2" s="7" t="s">
-        <v>58</v>
       </c>
       <c r="AM2" s="7" t="n">
         <v>11</v>
@@ -13415,27 +13043,27 @@
         <v>44</v>
       </c>
       <c r="AQ2" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" s="10" t="s">
         <v>62</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>44</v>
       </c>
       <c r="G3" s="10" t="s">
         <v>44</v>
@@ -13456,7 +13084,7 @@
         <v>64</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N3" s="8" t="s">
         <v>44</v>
@@ -13471,10 +13099,10 @@
         <v>44</v>
       </c>
       <c r="R3" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S3" s="6" t="n">
-        <v>0.4398</v>
+        <v>0.9509</v>
       </c>
       <c r="T3" s="7" t="s">
         <v>44</v>
@@ -13489,13 +13117,13 @@
         <v>44</v>
       </c>
       <c r="X3" s="7" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="Y3" s="7" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="Z3" s="7" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="AA3" s="7" t="s">
         <v>44</v>
@@ -13504,14 +13132,14 @@
         <v>44</v>
       </c>
       <c r="AC3" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD3" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE3" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="AD3" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE3" s="7" t="s">
-        <v>54</v>
-      </c>
       <c r="AF3" s="7" t="s">
         <v>44</v>
       </c>
@@ -13522,16 +13150,16 @@
         <v>44</v>
       </c>
       <c r="AI3" s="7" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="AJ3" s="7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="AK3" s="7" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="AL3" s="7" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AM3" s="7" t="n">
         <v>14</v>
@@ -13546,21 +13174,21 @@
         <v>44</v>
       </c>
       <c r="AQ3" s="7" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>44</v>
@@ -13578,28 +13206,28 @@
         <v>44</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K4" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="O4" s="8" t="s">
         <v>44</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="R4" s="6" t="n">
         <v>4</v>
@@ -13620,28 +13248,28 @@
         <v>44</v>
       </c>
       <c r="X4" s="7" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Y4" s="7" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="Z4" s="7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AA4" s="7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="AB4" s="7" t="s">
         <v>44</v>
       </c>
       <c r="AC4" s="7" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AD4" s="7" t="s">
         <v>44</v>
       </c>
       <c r="AE4" s="7" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AF4" s="7" t="s">
         <v>44</v>
@@ -13653,16 +13281,16 @@
         <v>44</v>
       </c>
       <c r="AI4" s="7" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AJ4" s="7" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AK4" s="7" t="s">
         <v>44</v>
       </c>
       <c r="AL4" s="7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AM4" s="7" t="n">
         <v>12</v>
@@ -13677,21 +13305,21 @@
         <v>44</v>
       </c>
       <c r="AQ4" s="7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>44</v>
@@ -13709,28 +13337,28 @@
         <v>44</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K5" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L5" s="10" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="N5" s="8" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="O5" s="8" t="s">
         <v>44</v>
       </c>
       <c r="P5" s="8" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Q5" s="8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="R5" s="6" t="n">
         <v>4</v>
@@ -13742,7 +13370,7 @@
         <v>44</v>
       </c>
       <c r="U5" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="V5" s="7" t="s">
         <v>44</v>
@@ -13751,28 +13379,28 @@
         <v>44</v>
       </c>
       <c r="X5" s="7" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Y5" s="7" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="Z5" s="7" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AA5" s="7" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="AB5" s="7" t="s">
         <v>44</v>
       </c>
       <c r="AC5" s="7" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AD5" s="7" t="s">
         <v>44</v>
       </c>
       <c r="AE5" s="7" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AF5" s="7" t="s">
         <v>44</v>
@@ -13784,16 +13412,16 @@
         <v>44</v>
       </c>
       <c r="AI5" s="7" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="AJ5" s="7" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="AK5" s="7" t="s">
         <v>44</v>
       </c>
       <c r="AL5" s="7" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="AM5" s="7" t="n">
         <v>4</v>
@@ -13808,21 +13436,21 @@
         <v>44</v>
       </c>
       <c r="AQ5" s="7" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>44</v>
@@ -13840,28 +13468,28 @@
         <v>44</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K6" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L6" s="10" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="O6" s="8" t="s">
         <v>44</v>
       </c>
       <c r="P6" s="8" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="Q6" s="8" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="R6" s="6" t="n">
         <v>4</v>
@@ -13873,7 +13501,7 @@
         <v>44</v>
       </c>
       <c r="U6" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="V6" s="7" t="s">
         <v>44</v>
@@ -13882,29 +13510,29 @@
         <v>44</v>
       </c>
       <c r="X6" s="7" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Y6" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z6" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA6" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="Z6" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="AA6" s="7" t="s">
-        <v>111</v>
-      </c>
       <c r="AB6" s="7" t="s">
         <v>44</v>
       </c>
       <c r="AC6" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD6" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE6" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="AD6" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE6" s="7" t="s">
-        <v>54</v>
-      </c>
       <c r="AF6" s="7" t="s">
         <v>44</v>
       </c>
@@ -13915,16 +13543,16 @@
         <v>44</v>
       </c>
       <c r="AI6" s="7" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="AJ6" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="AK6" s="7" t="s">
         <v>44</v>
       </c>
       <c r="AL6" s="7" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="AM6" s="7" t="n">
         <v>3</v>
@@ -13939,27 +13567,27 @@
         <v>44</v>
       </c>
       <c r="AQ6" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>44</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>122</v>
+        <v>44</v>
       </c>
       <c r="G7" s="10" t="s">
         <v>44</v>
@@ -13971,16 +13599,16 @@
         <v>44</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K7" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>124</v>
+        <v>64</v>
       </c>
       <c r="M7" s="11" t="s">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="N7" s="8" t="s">
         <v>44</v>
@@ -13998,7 +13626,7 @@
         <v>3</v>
       </c>
       <c r="S7" s="6" t="n">
-        <v>0.8314</v>
+        <v>0.5934</v>
       </c>
       <c r="T7" s="7" t="s">
         <v>44</v>
@@ -14013,49 +13641,49 @@
         <v>44</v>
       </c>
       <c r="X7" s="7" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="Y7" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z7" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA7" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB7" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC7" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD7" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE7" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="AF7" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG7" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH7" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI7" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="Z7" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="AA7" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB7" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC7" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="AD7" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE7" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="AF7" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AG7" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH7" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI7" s="7" t="s">
+      <c r="AJ7" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="AJ7" s="7" t="s">
+      <c r="AK7" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="AK7" s="7" t="s">
+      <c r="AL7" s="7" t="s">
         <v>129</v>
-      </c>
-      <c r="AL7" s="7" t="s">
-        <v>130</v>
       </c>
       <c r="AM7" s="7" t="n">
         <v>22</v>
@@ -14070,27 +13698,27 @@
         <v>44</v>
       </c>
       <c r="AQ7" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="10" t="s">
         <v>134</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>135</v>
       </c>
       <c r="G8" s="10" t="s">
         <v>44</v>
@@ -14102,16 +13730,16 @@
         <v>44</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K8" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>124</v>
+        <v>64</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="N8" s="8" t="s">
         <v>44</v>
@@ -14129,7 +13757,7 @@
         <v>3</v>
       </c>
       <c r="S8" s="6" t="n">
-        <v>0.982</v>
+        <v>0.9775</v>
       </c>
       <c r="T8" s="7" t="s">
         <v>44</v>
@@ -14144,13 +13772,13 @@
         <v>44</v>
       </c>
       <c r="X8" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="Y8" s="7" t="s">
-        <v>126</v>
+        <v>67</v>
       </c>
       <c r="Z8" s="7" t="s">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="AA8" s="7" t="s">
         <v>44</v>
@@ -14159,14 +13787,14 @@
         <v>44</v>
       </c>
       <c r="AC8" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD8" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="AD8" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE8" s="7" t="s">
-        <v>54</v>
-      </c>
       <c r="AF8" s="7" t="s">
         <v>44</v>
       </c>
@@ -14177,16 +13805,16 @@
         <v>44</v>
       </c>
       <c r="AI8" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="AJ8" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="AJ8" s="7" t="s">
+      <c r="AK8" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="AK8" s="7" t="s">
+      <c r="AL8" s="7" t="s">
         <v>139</v>
-      </c>
-      <c r="AL8" s="7" t="s">
-        <v>140</v>
       </c>
       <c r="AM8" s="7" t="n">
         <v>25</v>
@@ -14201,21 +13829,21 @@
         <v>44</v>
       </c>
       <c r="AQ8" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="5" t="s">
         <v>143</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>144</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>44</v>
@@ -14233,16 +13861,16 @@
         <v>44</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K9" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N9" s="8" t="s">
         <v>44</v>
@@ -14260,64 +13888,64 @@
         <v>1</v>
       </c>
       <c r="S9" s="6" t="n">
-        <v>0.4289</v>
+        <v>0.4784</v>
       </c>
       <c r="T9" s="7" t="s">
         <v>44</v>
       </c>
       <c r="U9" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="V9" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="W9" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="X9" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="Y9" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z9" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA9" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB9" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC9" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD9" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE9" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="AF9" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG9" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH9" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI9" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="V9" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="W9" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="X9" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="Y9" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z9" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="AA9" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB9" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC9" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="AD9" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE9" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="AF9" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AG9" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH9" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI9" s="7" t="s">
+      <c r="AJ9" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="AJ9" s="7" t="s">
+      <c r="AK9" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="AK9" s="7" t="s">
+      <c r="AL9" s="7" t="s">
         <v>150</v>
-      </c>
-      <c r="AL9" s="7" t="s">
-        <v>151</v>
       </c>
       <c r="AM9" s="7" t="n">
         <v>3</v>
@@ -14332,21 +13960,21 @@
         <v>44</v>
       </c>
       <c r="AQ9" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="5" t="s">
+      <c r="D10" s="5" t="s">
         <v>154</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>155</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>44</v>
@@ -14364,16 +13992,16 @@
         <v>44</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K10" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L10" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="M10" s="11" t="s">
         <v>157</v>
-      </c>
-      <c r="M10" s="11" t="s">
-        <v>158</v>
       </c>
       <c r="N10" s="8" t="s">
         <v>44</v>
@@ -14397,7 +14025,7 @@
         <v>44</v>
       </c>
       <c r="U10" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="V10" s="7" t="s">
         <v>44</v>
@@ -14406,49 +14034,49 @@
         <v>44</v>
       </c>
       <c r="X10" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="Y10" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z10" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="AA10" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="Y10" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z10" s="7" t="s">
+      <c r="AB10" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC10" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="AA10" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="AB10" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC10" s="7" t="s">
+      <c r="AD10" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="AD10" s="7" t="s">
+      <c r="AE10" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="AE10" s="7" t="s">
+      <c r="AF10" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="AF10" s="7" t="s">
+      <c r="AG10" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH10" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI10" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="AG10" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH10" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI10" s="7" t="s">
+      <c r="AJ10" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="AJ10" s="7" t="s">
+      <c r="AK10" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="AK10" s="7" t="s">
+      <c r="AL10" s="7" t="s">
         <v>165</v>
-      </c>
-      <c r="AL10" s="7" t="s">
-        <v>166</v>
       </c>
       <c r="AM10" s="7" t="n">
         <v>2</v>
@@ -14463,27 +14091,27 @@
         <v>44</v>
       </c>
       <c r="AQ10" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" s="5" t="s">
+      <c r="D11" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="E11" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" s="10" t="s">
         <v>170</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>171</v>
       </c>
       <c r="G11" s="10" t="s">
         <v>44</v>
@@ -14495,16 +14123,16 @@
         <v>44</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K11" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L11" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="M11" s="11" t="s">
         <v>173</v>
-      </c>
-      <c r="M11" s="11" t="s">
-        <v>174</v>
       </c>
       <c r="N11" s="8" t="s">
         <v>44</v>
@@ -14528,7 +14156,7 @@
         <v>44</v>
       </c>
       <c r="U11" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="V11" s="7" t="s">
         <v>44</v>
@@ -14537,49 +14165,49 @@
         <v>44</v>
       </c>
       <c r="X11" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="Y11" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="Z11" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="AA11" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB11" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC11" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD11" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE11" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="AF11" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG11" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH11" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI11" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="Z11" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="AA11" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB11" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC11" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="AD11" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE11" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="AF11" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AG11" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH11" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI11" s="7" t="s">
+      <c r="AJ11" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="AJ11" s="7" t="s">
+      <c r="AK11" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="AK11" s="7" t="s">
+      <c r="AL11" s="7" t="s">
         <v>178</v>
-      </c>
-      <c r="AL11" s="7" t="s">
-        <v>179</v>
       </c>
       <c r="AM11" s="7" t="n">
         <v>1</v>
@@ -14594,27 +14222,27 @@
         <v>44</v>
       </c>
       <c r="AQ11" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="5" t="s">
+      <c r="D12" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="E12" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F12" s="10" t="s">
         <v>183</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="G12" s="10" t="s">
         <v>44</v>
@@ -14626,16 +14254,16 @@
         <v>44</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K12" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L12" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="M12" s="11" t="s">
         <v>173</v>
-      </c>
-      <c r="M12" s="11" t="s">
-        <v>174</v>
       </c>
       <c r="N12" s="8" t="s">
         <v>44</v>
@@ -14659,7 +14287,7 @@
         <v>44</v>
       </c>
       <c r="U12" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="V12" s="7" t="s">
         <v>44</v>
@@ -14668,13 +14296,13 @@
         <v>44</v>
       </c>
       <c r="X12" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="Y12" s="7" t="s">
         <v>44</v>
       </c>
       <c r="Z12" s="7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AA12" s="7" t="s">
         <v>44</v>
@@ -14683,14 +14311,14 @@
         <v>44</v>
       </c>
       <c r="AC12" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD12" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE12" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="AD12" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE12" s="7" t="s">
-        <v>54</v>
-      </c>
       <c r="AF12" s="7" t="s">
         <v>44</v>
       </c>
@@ -14701,16 +14329,16 @@
         <v>44</v>
       </c>
       <c r="AI12" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="AJ12" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="AJ12" s="7" t="s">
+      <c r="AK12" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="AK12" s="7" t="s">
+      <c r="AL12" s="7" t="s">
         <v>188</v>
-      </c>
-      <c r="AL12" s="7" t="s">
-        <v>189</v>
       </c>
       <c r="AM12" s="7" t="n">
         <v>1</v>
@@ -14725,21 +14353,21 @@
         <v>44</v>
       </c>
       <c r="AQ12" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="5" t="s">
+      <c r="D13" s="5" t="s">
         <v>192</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>193</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>44</v>
@@ -14757,28 +14385,28 @@
         <v>44</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="K13" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="N13" s="8" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="O13" s="8" t="s">
         <v>44</v>
       </c>
       <c r="P13" s="8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="Q13" s="8" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="R13" s="6" t="n">
         <v>4</v>
@@ -14799,28 +14427,28 @@
         <v>44</v>
       </c>
       <c r="X13" s="7" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Y13" s="7" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="Z13" s="7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AA13" s="7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="AB13" s="7" t="s">
         <v>44</v>
       </c>
       <c r="AC13" s="7" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AD13" s="7" t="s">
         <v>44</v>
       </c>
       <c r="AE13" s="7" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AF13" s="7" t="s">
         <v>44</v>
@@ -14832,16 +14460,16 @@
         <v>44</v>
       </c>
       <c r="AI13" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="AJ13" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="AJ13" s="7" t="s">
-        <v>196</v>
-      </c>
       <c r="AK13" s="7" t="s">
         <v>44</v>
       </c>
       <c r="AL13" s="7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AM13" s="7" t="n">
         <v>10</v>
@@ -14856,21 +14484,21 @@
         <v>44</v>
       </c>
       <c r="AQ13" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="14" ht="25" customHeight="1">
       <c r="A14" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="5" t="s">
+      <c r="D14" s="5" t="s">
         <v>199</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>200</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>44</v>
@@ -14888,28 +14516,28 @@
         <v>44</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K14" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L14" s="10" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="N14" s="8" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="O14" s="8" t="s">
         <v>44</v>
       </c>
       <c r="P14" s="8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="Q14" s="8" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="R14" s="6" t="n">
         <v>4</v>
@@ -14930,28 +14558,28 @@
         <v>44</v>
       </c>
       <c r="X14" s="7" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Y14" s="7" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="Z14" s="7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AA14" s="7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="AB14" s="7" t="s">
         <v>44</v>
       </c>
       <c r="AC14" s="7" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AD14" s="7" t="s">
         <v>44</v>
       </c>
       <c r="AE14" s="7" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AF14" s="7" t="s">
         <v>44</v>
@@ -14963,16 +14591,16 @@
         <v>44</v>
       </c>
       <c r="AI14" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="AJ14" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="AJ14" s="7" t="s">
-        <v>203</v>
-      </c>
       <c r="AK14" s="7" t="s">
         <v>44</v>
       </c>
       <c r="AL14" s="7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AM14" s="7" t="n">
         <v>10</v>
@@ -14987,21 +14615,21 @@
         <v>44</v>
       </c>
       <c r="AQ14" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="15" ht="25" customHeight="1">
       <c r="A15" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="5" t="s">
+      <c r="D15" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>207</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>44</v>
@@ -15019,16 +14647,16 @@
         <v>44</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="K15" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="M15" s="11" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="N15" s="8" t="s">
         <v>44</v>
@@ -15043,16 +14671,16 @@
         <v>44</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S15" s="6" t="n">
-        <v>0.6255</v>
+        <v>0.3827</v>
       </c>
       <c r="T15" s="7" t="s">
         <v>44</v>
       </c>
       <c r="U15" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="V15" s="7" t="s">
         <v>44</v>
@@ -15061,49 +14689,49 @@
         <v>44</v>
       </c>
       <c r="X15" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Y15" s="7" t="s">
         <v>44</v>
       </c>
       <c r="Z15" s="7" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="AA15" s="7" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="AB15" s="7" t="s">
         <v>44</v>
       </c>
       <c r="AC15" s="7" t="s">
-        <v>159</v>
+        <v>52</v>
       </c>
       <c r="AD15" s="7" t="s">
-        <v>160</v>
+        <v>44</v>
       </c>
       <c r="AE15" s="7" t="s">
-        <v>161</v>
+        <v>53</v>
       </c>
       <c r="AF15" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG15" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH15" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI15" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="AJ15" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="AG15" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH15" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI15" s="7" t="s">
+      <c r="AK15" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="AJ15" s="7" t="s">
+      <c r="AL15" s="7" t="s">
         <v>211</v>
-      </c>
-      <c r="AK15" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="AL15" s="7" t="s">
-        <v>213</v>
       </c>
       <c r="AM15" s="7" t="n">
         <v>3</v>
@@ -15118,21 +14746,21 @@
         <v>44</v>
       </c>
       <c r="AQ15" s="7" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16" ht="25" customHeight="1">
       <c r="A16" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>215</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>217</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>44</v>
@@ -15150,16 +14778,16 @@
         <v>44</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="K16" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L16" s="10" t="s">
-        <v>146</v>
+        <v>217</v>
       </c>
       <c r="M16" s="11" t="s">
-        <v>146</v>
+        <v>217</v>
       </c>
       <c r="N16" s="8" t="s">
         <v>44</v>
@@ -15177,13 +14805,13 @@
         <v>1</v>
       </c>
       <c r="S16" s="6" t="n">
-        <v>0.3866</v>
+        <v>0.3283</v>
       </c>
       <c r="T16" s="7" t="s">
         <v>44</v>
       </c>
       <c r="U16" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="V16" s="7" t="s">
         <v>44</v>
@@ -15192,13 +14820,13 @@
         <v>44</v>
       </c>
       <c r="X16" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Y16" s="7" t="s">
         <v>44</v>
       </c>
       <c r="Z16" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AA16" s="7" t="s">
         <v>44</v>
@@ -15207,14 +14835,14 @@
         <v>44</v>
       </c>
       <c r="AC16" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD16" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE16" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="AD16" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE16" s="7" t="s">
-        <v>54</v>
-      </c>
       <c r="AF16" s="7" t="s">
         <v>44</v>
       </c>
@@ -15225,16 +14853,16 @@
         <v>44</v>
       </c>
       <c r="AI16" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="AJ16" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="AJ16" s="7" t="s">
+      <c r="AK16" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="AK16" s="7" t="s">
+      <c r="AL16" s="7" t="s">
         <v>221</v>
-      </c>
-      <c r="AL16" s="7" t="s">
-        <v>222</v>
       </c>
       <c r="AM16" s="7" t="n">
         <v>3</v>
@@ -15249,21 +14877,21 @@
         <v>44</v>
       </c>
       <c r="AQ16" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="17" ht="25" customHeight="1">
       <c r="A17" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17" s="5" t="s">
+      <c r="D17" s="5" t="s">
         <v>225</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>226</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>44</v>
@@ -15281,16 +14909,16 @@
         <v>44</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="K17" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="M17" s="11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N17" s="8" t="s">
         <v>44</v>
@@ -15308,13 +14936,13 @@
         <v>1</v>
       </c>
       <c r="S17" s="6" t="n">
-        <v>0.3096</v>
+        <v>0.4426</v>
       </c>
       <c r="T17" s="7" t="s">
         <v>44</v>
       </c>
       <c r="U17" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="V17" s="7" t="s">
         <v>44</v>
@@ -15323,13 +14951,13 @@
         <v>44</v>
       </c>
       <c r="X17" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Y17" s="7" t="s">
         <v>44</v>
       </c>
       <c r="Z17" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AA17" s="7" t="s">
         <v>44</v>
@@ -15338,14 +14966,14 @@
         <v>44</v>
       </c>
       <c r="AC17" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD17" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE17" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="AD17" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE17" s="7" t="s">
-        <v>54</v>
-      </c>
       <c r="AF17" s="7" t="s">
         <v>44</v>
       </c>
@@ -15356,16 +14984,16 @@
         <v>44</v>
       </c>
       <c r="AI17" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="AJ17" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="AJ17" s="7" t="s">
+      <c r="AK17" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="AK17" s="7" t="s">
+      <c r="AL17" s="7" t="s">
         <v>230</v>
-      </c>
-      <c r="AL17" s="7" t="s">
-        <v>231</v>
       </c>
       <c r="AM17" s="7" t="n">
         <v>3</v>
@@ -15380,21 +15008,21 @@
         <v>44</v>
       </c>
       <c r="AQ17" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="18" ht="25" customHeight="1">
       <c r="A18" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" s="5" t="s">
+      <c r="D18" s="5" t="s">
         <v>234</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>235</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>44</v>
@@ -15412,16 +15040,16 @@
         <v>44</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="K18" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L18" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="M18" s="11" t="s">
         <v>237</v>
-      </c>
-      <c r="M18" s="11" t="s">
-        <v>238</v>
       </c>
       <c r="N18" s="8" t="s">
         <v>44</v>
@@ -15439,13 +15067,13 @@
         <v>3</v>
       </c>
       <c r="S18" s="6" t="n">
-        <v>0.7303</v>
+        <v>0.6202</v>
       </c>
       <c r="T18" s="7" t="s">
         <v>44</v>
       </c>
       <c r="U18" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="V18" s="7" t="s">
         <v>44</v>
@@ -15454,49 +15082,49 @@
         <v>44</v>
       </c>
       <c r="X18" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="Y18" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z18" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="AA18" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="Y18" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z18" s="7" t="s">
+      <c r="AB18" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC18" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="AD18" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="AE18" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="AF18" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="AA18" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="AB18" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC18" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="AD18" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="AE18" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="AF18" s="7" t="s">
+      <c r="AG18" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH18" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI18" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="AG18" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH18" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI18" s="7" t="s">
+      <c r="AJ18" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="AJ18" s="7" t="s">
+      <c r="AK18" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="AK18" s="7" t="s">
+      <c r="AL18" s="7" t="s">
         <v>242</v>
-      </c>
-      <c r="AL18" s="7" t="s">
-        <v>243</v>
       </c>
       <c r="AM18" s="7" t="n">
         <v>19</v>
@@ -15511,21 +15139,21 @@
         <v>44</v>
       </c>
       <c r="AQ18" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="19" ht="25" customHeight="1">
       <c r="A19" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" s="5" t="s">
+      <c r="D19" s="5" t="s">
         <v>246</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>247</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>44</v>
@@ -15543,16 +15171,16 @@
         <v>44</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K19" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L19" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="M19" s="11" t="s">
         <v>237</v>
-      </c>
-      <c r="M19" s="11" t="s">
-        <v>238</v>
       </c>
       <c r="N19" s="8" t="s">
         <v>44</v>
@@ -15570,13 +15198,13 @@
         <v>3</v>
       </c>
       <c r="S19" s="6" t="n">
-        <v>0.5969</v>
+        <v>0.5796</v>
       </c>
       <c r="T19" s="7" t="s">
         <v>44</v>
       </c>
       <c r="U19" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="V19" s="7" t="s">
         <v>44</v>
@@ -15585,49 +15213,49 @@
         <v>44</v>
       </c>
       <c r="X19" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="Y19" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z19" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="AA19" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="Y19" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z19" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="AA19" s="7" t="s">
-        <v>147</v>
-      </c>
       <c r="AB19" s="7" t="s">
         <v>44</v>
       </c>
       <c r="AC19" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="AD19" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="AD19" s="7" t="s">
+      <c r="AE19" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="AE19" s="7" t="s">
-        <v>161</v>
-      </c>
       <c r="AF19" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="AG19" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH19" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI19" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="AG19" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH19" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI19" s="7" t="s">
+      <c r="AJ19" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="AJ19" s="7" t="s">
+      <c r="AK19" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="AK19" s="7" t="s">
+      <c r="AL19" s="7" t="s">
         <v>252</v>
-      </c>
-      <c r="AL19" s="7" t="s">
-        <v>253</v>
       </c>
       <c r="AM19" s="7" t="n">
         <v>19</v>
@@ -15642,21 +15270,21 @@
         <v>44</v>
       </c>
       <c r="AQ19" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="20" ht="25" customHeight="1">
       <c r="A20" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="D20" s="5" t="s">
         <v>255</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>256</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>44</v>
@@ -15674,25 +15302,25 @@
         <v>44</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K20" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L20" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="M20" s="11" t="s">
         <v>258</v>
       </c>
-      <c r="M20" s="11" t="s">
+      <c r="N20" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="N20" s="8" t="s">
-        <v>260</v>
-      </c>
       <c r="O20" s="8" t="s">
         <v>44</v>
       </c>
       <c r="P20" s="8" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Q20" s="8" t="s">
         <v>44</v>
@@ -15716,49 +15344,49 @@
         <v>44</v>
       </c>
       <c r="X20" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="Y20" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z20" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="AA20" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="Y20" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z20" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="AA20" s="7" t="s">
-        <v>147</v>
-      </c>
       <c r="AB20" s="7" t="s">
         <v>44</v>
       </c>
       <c r="AC20" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AD20" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="AE20" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="AF20" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="AE20" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="AF20" s="7" t="s">
+      <c r="AG20" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH20" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI20" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="AG20" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH20" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI20" s="7" t="s">
+      <c r="AJ20" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="AJ20" s="7" t="s">
+      <c r="AK20" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="AK20" s="7" t="s">
+      <c r="AL20" s="7" t="s">
         <v>265</v>
-      </c>
-      <c r="AL20" s="7" t="s">
-        <v>266</v>
       </c>
       <c r="AM20" s="7" t="n">
         <v>8</v>
@@ -15773,7 +15401,7 @@
         <v>44</v>
       </c>
       <c r="AQ20" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -15792,13 +15420,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C1" t="s">
         <v>268</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>269</v>
-      </c>
-      <c r="D1" t="s">
-        <v>270</v>
       </c>
       <c r="E1" t="s">
         <v>51</v>
@@ -15806,7 +15434,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B2" t="s">
         <v>37</v>
@@ -15818,12 +15446,12 @@
         <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B3" t="s">
         <v>37</v>
@@ -15835,12 +15463,12 @@
         <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B4" t="s">
         <v>37</v>
@@ -15852,12 +15480,12 @@
         <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B5" t="s">
         <v>37</v>
@@ -15869,12 +15497,12 @@
         <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B6" t="s">
         <v>37</v>
@@ -15886,12 +15514,12 @@
         <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B7" t="s">
         <v>37</v>
@@ -15903,12 +15531,12 @@
         <v>14</v>
       </c>
       <c r="E7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B8" t="s">
         <v>37</v>
@@ -15920,12 +15548,12 @@
         <v>14</v>
       </c>
       <c r="E8" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B9" t="s">
         <v>37</v>
@@ -15937,12 +15565,12 @@
         <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B10" t="s">
         <v>37</v>
@@ -15954,12 +15582,12 @@
         <v>14</v>
       </c>
       <c r="E10" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B11" t="s">
         <v>37</v>
@@ -15971,12 +15599,12 @@
         <v>14</v>
       </c>
       <c r="E11" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B12" t="s">
         <v>37</v>
@@ -15988,12 +15616,12 @@
         <v>14</v>
       </c>
       <c r="E12" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B13" t="s">
         <v>37</v>
@@ -16005,12 +15633,12 @@
         <v>14</v>
       </c>
       <c r="E13" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B14" t="s">
         <v>37</v>
@@ -16022,12 +15650,12 @@
         <v>14</v>
       </c>
       <c r="E14" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B15" t="s">
         <v>37</v>
@@ -16039,12 +15667,12 @@
         <v>14</v>
       </c>
       <c r="E15" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B16" t="s">
         <v>37</v>
@@ -16056,12 +15684,12 @@
         <v>10</v>
       </c>
       <c r="E16" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s">
         <v>37</v>
@@ -16073,12 +15701,12 @@
         <v>10</v>
       </c>
       <c r="E17" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B18" t="s">
         <v>37</v>
@@ -16090,12 +15718,12 @@
         <v>10</v>
       </c>
       <c r="E18" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B19" t="s">
         <v>37</v>
@@ -16107,12 +15735,12 @@
         <v>10</v>
       </c>
       <c r="E19" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B20" t="s">
         <v>37</v>
@@ -16124,12 +15752,12 @@
         <v>10</v>
       </c>
       <c r="E20" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B21" t="s">
         <v>37</v>
@@ -16141,12 +15769,12 @@
         <v>10</v>
       </c>
       <c r="E21" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B22" t="s">
         <v>37</v>
@@ -16158,12 +15786,12 @@
         <v>10</v>
       </c>
       <c r="E22" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B23" t="s">
         <v>37</v>
@@ -16175,12 +15803,12 @@
         <v>10</v>
       </c>
       <c r="E23" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B24" t="s">
         <v>37</v>
@@ -16192,12 +15820,12 @@
         <v>10</v>
       </c>
       <c r="E24" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B25" t="s">
         <v>37</v>
@@ -16209,12 +15837,12 @@
         <v>10</v>
       </c>
       <c r="E25" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B26" t="s">
         <v>37</v>
@@ -16226,12 +15854,12 @@
         <v>8</v>
       </c>
       <c r="E26" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B27" t="s">
         <v>37</v>
@@ -16243,12 +15871,12 @@
         <v>8</v>
       </c>
       <c r="E27" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B28" t="s">
         <v>37</v>
@@ -16260,12 +15888,12 @@
         <v>8</v>
       </c>
       <c r="E28" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B29" t="s">
         <v>37</v>
@@ -16277,12 +15905,12 @@
         <v>8</v>
       </c>
       <c r="E29" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B30" t="s">
         <v>37</v>
@@ -16294,12 +15922,12 @@
         <v>8</v>
       </c>
       <c r="E30" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B31" t="s">
         <v>37</v>
@@ -16311,12 +15939,12 @@
         <v>8</v>
       </c>
       <c r="E31" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B32" t="s">
         <v>37</v>
@@ -16328,12 +15956,12 @@
         <v>8</v>
       </c>
       <c r="E32" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B33" t="s">
         <v>37</v>
@@ -16345,7 +15973,7 @@
         <v>8</v>
       </c>
       <c r="E33" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
   </sheetData>
